--- a/src/attributions/attributions_saliency_traj_88.xlsx
+++ b/src/attributions/attributions_saliency_traj_88.xlsx
@@ -1568,571 +1568,571 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.148848514276324e-05</v>
+        <v>0.1747926771640778</v>
       </c>
       <c r="B3" t="n">
-        <v>3.975947038270533e-08</v>
+        <v>0.02850190363824368</v>
       </c>
       <c r="C3" t="n">
-        <v>7.120841473806649e-05</v>
+        <v>0.08555925637483597</v>
       </c>
       <c r="D3" t="n">
-        <v>2.147802115359809e-05</v>
+        <v>0.04976065829396248</v>
       </c>
       <c r="E3" t="n">
-        <v>1.398254198647919e-06</v>
+        <v>0.164785698056221</v>
       </c>
       <c r="F3" t="n">
-        <v>1.90708724403521e-05</v>
+        <v>0.08675548434257507</v>
       </c>
       <c r="G3" t="n">
-        <v>1.077356864698231e-05</v>
+        <v>0.02621055021882057</v>
       </c>
       <c r="H3" t="n">
-        <v>2.878120176319499e-05</v>
+        <v>0.002985644154250622</v>
       </c>
       <c r="I3" t="n">
-        <v>6.585466326214373e-05</v>
+        <v>0.0863988921046257</v>
       </c>
       <c r="J3" t="n">
-        <v>4.006327435490675e-05</v>
+        <v>0.1709787845611572</v>
       </c>
       <c r="K3" t="n">
-        <v>3.312905391794629e-05</v>
+        <v>0.004288175143301487</v>
       </c>
       <c r="L3" t="n">
-        <v>5.501457053469494e-05</v>
+        <v>0.06181260198354721</v>
       </c>
       <c r="M3" t="n">
-        <v>4.93610386911314e-05</v>
+        <v>0.04984281212091446</v>
       </c>
       <c r="N3" t="n">
-        <v>2.479309114278294e-05</v>
+        <v>0.1212552785873413</v>
       </c>
       <c r="O3" t="n">
-        <v>2.178281283704564e-05</v>
+        <v>0.1105473712086678</v>
       </c>
       <c r="P3" t="n">
-        <v>8.15859530121088e-05</v>
+        <v>0.06093697994947433</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.322204934695037e-05</v>
+        <v>0.07142245769500732</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0001340152812190354</v>
+        <v>0.07240915298461914</v>
       </c>
       <c r="S3" t="n">
-        <v>1.917255758598913e-06</v>
+        <v>0.004945190157741308</v>
       </c>
       <c r="T3" t="n">
-        <v>1.092835191229824e-05</v>
+        <v>0.06137543916702271</v>
       </c>
       <c r="U3" t="n">
-        <v>2.291361488460097e-05</v>
+        <v>0.03146393597126007</v>
       </c>
       <c r="V3" t="n">
-        <v>6.858545384602621e-05</v>
+        <v>0.0211707167327404</v>
       </c>
       <c r="W3" t="n">
-        <v>4.668491237680428e-05</v>
+        <v>0.08432306349277496</v>
       </c>
       <c r="X3" t="n">
-        <v>4.650032497011125e-05</v>
+        <v>0.06886960566043854</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.42792336596176e-05</v>
+        <v>0.03040209040045738</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0001036629182635807</v>
+        <v>0.03890886157751083</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.445020097889937e-05</v>
+        <v>0.009345687925815582</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.634422895032912e-05</v>
+        <v>0.03673695772886276</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.145618352893507e-05</v>
+        <v>0.04292654991149902</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.082501957076602e-05</v>
+        <v>0.005465500056743622</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.835117836890277e-05</v>
+        <v>0.01348506845533848</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.933227733592503e-05</v>
+        <v>0.03589114174246788</v>
       </c>
       <c r="AG3" t="n">
-        <v>7.950610597617924e-05</v>
+        <v>0.01442479807883501</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.146784208889585e-05</v>
+        <v>0.003833438269793987</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.217335531895515e-05</v>
+        <v>0.04204921796917915</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.770419450826012e-05</v>
+        <v>0.03619669377803802</v>
       </c>
       <c r="AK3" t="n">
-        <v>9.449743174627656e-07</v>
+        <v>0.04572665691375732</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.809931877185591e-05</v>
+        <v>0.08484599739313126</v>
       </c>
       <c r="AM3" t="n">
-        <v>8.210339728975669e-05</v>
+        <v>0.00888441875576973</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.370261038071476e-05</v>
+        <v>0.005602588411420584</v>
       </c>
       <c r="AO3" t="n">
-        <v>7.009100954746827e-05</v>
+        <v>0.06857246160507202</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.321487722336315e-06</v>
+        <v>0.01338005997240543</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.822913302225061e-06</v>
+        <v>0.01148196309804916</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.481067556596827e-05</v>
+        <v>0.03718241676688194</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.047365342150442e-05</v>
+        <v>0.00301201269030571</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.070316259050742e-05</v>
+        <v>0.07878700643777847</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.787225482985377e-05</v>
+        <v>0.05741110444068909</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0001386271615047008</v>
+        <v>0.002517811488360167</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.218573015648872e-05</v>
+        <v>0.03030194155871868</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0002348261186853051</v>
+        <v>0.1020108312368393</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.000146135498653166</v>
+        <v>0.07782425731420517</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.640009552123956e-05</v>
+        <v>0.02574279345571995</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0001052117149811238</v>
+        <v>0.03811094909906387</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0001460253988625482</v>
+        <v>0.0754464864730835</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.313617682782933e-05</v>
+        <v>0.01785659231245518</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.351276816625614e-05</v>
+        <v>0.03326709941029549</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.895340291317552e-05</v>
+        <v>0.02720652334392071</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.949428719351999e-05</v>
+        <v>0.01647778227925301</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.000127880834043026</v>
+        <v>0.006681437604129314</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.405711347819306e-05</v>
+        <v>0.0235828161239624</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.027829966915306e-05</v>
+        <v>0.02342662401497364</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0001150309763033874</v>
+        <v>0.06945430487394333</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0001255952956853434</v>
+        <v>0.0260541383177042</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.662738213781267e-05</v>
+        <v>0.01218256168067455</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0001095669504138641</v>
+        <v>0.04455468058586121</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.956951382453553e-05</v>
+        <v>0.007086364552378654</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.062698255642317e-05</v>
+        <v>0.0399794913828373</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.8377451649867e-05</v>
+        <v>0.04858298972249031</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0001087527125491761</v>
+        <v>0.003566289786249399</v>
       </c>
       <c r="BR3" t="n">
-        <v>9.516729733149987e-06</v>
+        <v>0.01212160941213369</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.464279042324051e-05</v>
+        <v>0.00927313044667244</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.842914444860071e-05</v>
+        <v>0.02634826675057411</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.126893600187032e-07</v>
+        <v>0.06986120343208313</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.152809848776087e-05</v>
+        <v>0.08918052911758423</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.139064913033508e-05</v>
+        <v>0.02010617963969707</v>
       </c>
       <c r="BX3" t="n">
-        <v>1.944910036399961e-05</v>
+        <v>0.01150952838361263</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.529334784019738e-05</v>
+        <v>0.1205800920724869</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.614422505255789e-05</v>
+        <v>0.01650075428187847</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.24822473077802e-06</v>
+        <v>0.02378352545201778</v>
       </c>
       <c r="CB3" t="n">
-        <v>1.974943734239787e-05</v>
+        <v>0.07769511640071869</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0001031706851790659</v>
+        <v>0.02460858784615993</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.730336746026296e-05</v>
+        <v>0.06023834645748138</v>
       </c>
       <c r="CE3" t="n">
-        <v>5.661437899107113e-05</v>
+        <v>0.01597608625888824</v>
       </c>
       <c r="CF3" t="n">
-        <v>1.635862099647056e-05</v>
+        <v>0.005594986490905285</v>
       </c>
       <c r="CG3" t="n">
-        <v>1.319334296567831e-05</v>
+        <v>0.00401917053386569</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.699002677924e-05</v>
+        <v>0.04182707518339157</v>
       </c>
       <c r="CI3" t="n">
-        <v>4.67611025669612e-05</v>
+        <v>0.001856329967267811</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.24264697660692e-05</v>
+        <v>0.005275759845972061</v>
       </c>
       <c r="CK3" t="n">
-        <v>2.640798265929334e-05</v>
+        <v>0.01230077166110277</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.118630552809918e-05</v>
+        <v>0.02165278419852257</v>
       </c>
       <c r="CM3" t="n">
-        <v>6.474301335401833e-05</v>
+        <v>0.05542517453432083</v>
       </c>
       <c r="CN3" t="n">
-        <v>4.519638969213702e-05</v>
+        <v>0.06447280943393707</v>
       </c>
       <c r="CO3" t="n">
-        <v>5.199173756409436e-06</v>
+        <v>0.07428643852472305</v>
       </c>
       <c r="CP3" t="n">
-        <v>4.800187525688671e-05</v>
+        <v>0.0571710579097271</v>
       </c>
       <c r="CQ3" t="n">
-        <v>6.60025398246944e-05</v>
+        <v>0.01541083864867687</v>
       </c>
       <c r="CR3" t="n">
-        <v>3.584540536394343e-05</v>
+        <v>0.002172783017158508</v>
       </c>
       <c r="CS3" t="n">
-        <v>1.177045032818569e-05</v>
+        <v>0.009342793375253677</v>
       </c>
       <c r="CT3" t="n">
-        <v>9.147867785941344e-06</v>
+        <v>0.01675416715443134</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.0001369777746731415</v>
+        <v>0.03291450440883636</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.176623482024297e-05</v>
+        <v>0.05530088767409325</v>
       </c>
       <c r="CW3" t="n">
-        <v>4.147351501160301e-05</v>
+        <v>0.02149419113993645</v>
       </c>
       <c r="CX3" t="n">
-        <v>2.655537537066266e-05</v>
+        <v>0.004904306028038263</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.005304056889145e-05</v>
+        <v>0.005211169831454754</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.310415882471716e-05</v>
+        <v>0.03579610958695412</v>
       </c>
       <c r="DA3" t="n">
-        <v>6.041143933543935e-05</v>
+        <v>0.006773679051548243</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.426037124474533e-05</v>
+        <v>0.01314981561154127</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.83305237442255e-05</v>
+        <v>0.003184431465342641</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.280507513001794e-05</v>
+        <v>0.01989210397005081</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.674001396168023e-05</v>
+        <v>0.08352936804294586</v>
       </c>
       <c r="DF3" t="n">
-        <v>9.402612340636551e-05</v>
+        <v>0.0007087206467986107</v>
       </c>
       <c r="DG3" t="n">
-        <v>9.337156370747834e-05</v>
+        <v>0.04850957170128822</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.000114079644845333</v>
+        <v>0.03531992435455322</v>
       </c>
       <c r="DI3" t="n">
-        <v>1.689438431640156e-05</v>
+        <v>0.07421816140413284</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.0001092543097911403</v>
+        <v>0.08887171745300293</v>
       </c>
       <c r="DK3" t="n">
-        <v>8.630506636109203e-05</v>
+        <v>0.01499008759856224</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0002294183796038851</v>
+        <v>0.01720580831170082</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0001399989414494485</v>
+        <v>0.07390455901622772</v>
       </c>
       <c r="DN3" t="n">
-        <v>3.956425643991679e-05</v>
+        <v>0.05140986666083336</v>
       </c>
       <c r="DO3" t="n">
-        <v>5.355821849661879e-05</v>
+        <v>0.02916466072201729</v>
       </c>
       <c r="DP3" t="n">
-        <v>4.006484959973022e-05</v>
+        <v>0.01253010053187609</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.16567753138952e-05</v>
+        <v>0.007899796590209007</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0001465938403271139</v>
+        <v>0.02498295903205872</v>
       </c>
       <c r="DS3" t="n">
-        <v>5.155163671588525e-05</v>
+        <v>0.02646581828594208</v>
       </c>
       <c r="DT3" t="n">
-        <v>3.8121834222693e-05</v>
+        <v>0.06370476633310318</v>
       </c>
       <c r="DU3" t="n">
-        <v>1.097994481824571e-05</v>
+        <v>0.007092208601534367</v>
       </c>
       <c r="DV3" t="n">
-        <v>6.576943178515648e-06</v>
+        <v>0.005831790156662464</v>
       </c>
       <c r="DW3" t="n">
-        <v>1.599897041160148e-05</v>
+        <v>0.006056963466107845</v>
       </c>
       <c r="DX3" t="n">
-        <v>3.566127270460129e-05</v>
+        <v>0.0004098981153219938</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.04058948031161e-06</v>
+        <v>0.01648734509944916</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.924181510228664e-05</v>
+        <v>0.11733128875494</v>
       </c>
       <c r="EA3" t="n">
-        <v>6.702409154968336e-05</v>
+        <v>0.07918073236942291</v>
       </c>
       <c r="EB3" t="n">
-        <v>6.969246169319376e-05</v>
+        <v>0.006911451928317547</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.240570029243827e-05</v>
+        <v>0.04439940303564072</v>
       </c>
       <c r="ED3" t="n">
-        <v>4.674770389101468e-05</v>
+        <v>0.05315369367599487</v>
       </c>
       <c r="EE3" t="n">
-        <v>8.415459160460159e-05</v>
+        <v>0.01916565746068954</v>
       </c>
       <c r="EF3" t="n">
-        <v>1.98296875169035e-05</v>
+        <v>0.02602319046854973</v>
       </c>
       <c r="EG3" t="n">
-        <v>5.910673644393682e-05</v>
+        <v>0.01611574552953243</v>
       </c>
       <c r="EH3" t="n">
-        <v>4.114011971978471e-05</v>
+        <v>0.02588755264878273</v>
       </c>
       <c r="EI3" t="n">
-        <v>3.017173003172502e-05</v>
+        <v>0.01094713807106018</v>
       </c>
       <c r="EJ3" t="n">
-        <v>2.106372630805708e-05</v>
+        <v>0.01316266600042582</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.0001356784632662311</v>
+        <v>0.02951802313327789</v>
       </c>
       <c r="EL3" t="n">
-        <v>1.532223905087449e-06</v>
+        <v>0.007932282984256744</v>
       </c>
       <c r="EM3" t="n">
-        <v>2.262653651996516e-05</v>
+        <v>0.014310572296381</v>
       </c>
       <c r="EN3" t="n">
-        <v>1.764138141879812e-05</v>
+        <v>0.03884937614202499</v>
       </c>
       <c r="EO3" t="n">
-        <v>1.005353442451451e-05</v>
+        <v>0.03593357279896736</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0001390223042108119</v>
+        <v>0.02083831652998924</v>
       </c>
       <c r="EQ3" t="n">
-        <v>2.698023308767006e-06</v>
+        <v>0.07494568824768066</v>
       </c>
       <c r="ER3" t="n">
-        <v>1.204219552164432e-05</v>
+        <v>0.0007081317016854882</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.0001046841862262227</v>
+        <v>0.04014988243579865</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.0001045229146257043</v>
+        <v>0.03305096551775932</v>
       </c>
       <c r="EU3" t="n">
-        <v>2.542205766076222e-05</v>
+        <v>0.002069678623229265</v>
       </c>
       <c r="EV3" t="n">
-        <v>4.937795165460557e-05</v>
+        <v>0.05457155779004097</v>
       </c>
       <c r="EW3" t="n">
-        <v>4.722137600765564e-05</v>
+        <v>0.05412743240594864</v>
       </c>
       <c r="EX3" t="n">
-        <v>1.619871363800485e-05</v>
+        <v>0.05614398792386055</v>
       </c>
       <c r="EY3" t="n">
-        <v>4.392525443108752e-05</v>
+        <v>0.02645531296730042</v>
       </c>
       <c r="EZ3" t="n">
-        <v>9.934404261002783e-06</v>
+        <v>0.009060808457434177</v>
       </c>
       <c r="FA3" t="n">
-        <v>1.713706114969682e-05</v>
+        <v>0.01494676899164915</v>
       </c>
       <c r="FB3" t="n">
-        <v>5.87250588068855e-06</v>
+        <v>0.04102429375052452</v>
       </c>
       <c r="FC3" t="n">
-        <v>4.64753175037913e-05</v>
+        <v>0.007232473231852055</v>
       </c>
       <c r="FD3" t="n">
-        <v>9.035468792717438e-06</v>
+        <v>0.02021374180912971</v>
       </c>
       <c r="FE3" t="n">
-        <v>3.95144488720689e-05</v>
+        <v>0.004374831914901733</v>
       </c>
       <c r="FF3" t="n">
-        <v>9.190046512230765e-06</v>
+        <v>0.02248268574476242</v>
       </c>
       <c r="FG3" t="n">
-        <v>4.418754542712122e-05</v>
+        <v>0.03755159303545952</v>
       </c>
       <c r="FH3" t="n">
-        <v>3.808584006037563e-05</v>
+        <v>0.0007411142578348517</v>
       </c>
       <c r="FI3" t="n">
-        <v>1.267153857043013e-05</v>
+        <v>0.04243152216076851</v>
       </c>
       <c r="FJ3" t="n">
-        <v>2.22166272578761e-05</v>
+        <v>0.07526334375143051</v>
       </c>
       <c r="FK3" t="n">
-        <v>1.864298974396661e-05</v>
+        <v>0.0294372234493494</v>
       </c>
       <c r="FL3" t="n">
-        <v>9.004042658489197e-05</v>
+        <v>0.04195849224925041</v>
       </c>
       <c r="FM3" t="n">
-        <v>2.157037670258433e-05</v>
+        <v>0.05481371283531189</v>
       </c>
       <c r="FN3" t="n">
-        <v>1.432878252671799e-05</v>
+        <v>0.003039887640625238</v>
       </c>
       <c r="FO3" t="n">
-        <v>7.614994501636829e-06</v>
+        <v>0.001546462997794151</v>
       </c>
       <c r="FP3" t="n">
-        <v>4.42238560935948e-05</v>
+        <v>0.0234459675848484</v>
       </c>
       <c r="FQ3" t="n">
-        <v>1.122799949371256e-05</v>
+        <v>0.02593085542321205</v>
       </c>
       <c r="FR3" t="n">
-        <v>7.136745261959732e-05</v>
+        <v>0.0671364814043045</v>
       </c>
       <c r="FS3" t="n">
-        <v>4.696377800428309e-06</v>
+        <v>0.002851793542504311</v>
       </c>
       <c r="FT3" t="n">
-        <v>8.466557483188808e-05</v>
+        <v>0.06751572340726852</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.0001857576862676069</v>
+        <v>0.04642681404948235</v>
       </c>
       <c r="FV3" t="n">
-        <v>4.36869595432654e-05</v>
+        <v>0.007222886197268963</v>
       </c>
       <c r="FW3" t="n">
-        <v>6.553359708050266e-05</v>
+        <v>0.0152177307754755</v>
       </c>
       <c r="FX3" t="n">
-        <v>9.828346810536459e-05</v>
+        <v>0.07808622717857361</v>
       </c>
       <c r="FY3" t="n">
-        <v>3.13960226776544e-05</v>
+        <v>0.03127774223685265</v>
       </c>
       <c r="FZ3" t="n">
-        <v>7.238826947286725e-05</v>
+        <v>0.05486747249960899</v>
       </c>
       <c r="GA3" t="n">
-        <v>3.431277582421899e-05</v>
+        <v>0.01585939340293407</v>
       </c>
       <c r="GB3" t="n">
-        <v>1.526275627838913e-05</v>
+        <v>0.02601906657218933</v>
       </c>
       <c r="GC3" t="n">
-        <v>1.836341539274144e-06</v>
+        <v>0.06340380012989044</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.0001580609969096258</v>
+        <v>0.03871003910899162</v>
       </c>
       <c r="GE3" t="n">
-        <v>1.440431788068963e-05</v>
+        <v>0.003945070318877697</v>
       </c>
       <c r="GF3" t="n">
-        <v>4.014405931229703e-05</v>
+        <v>0.004886835813522339</v>
       </c>
       <c r="GG3" t="n">
-        <v>2.984654383908492e-05</v>
+        <v>0.0209921058267355</v>
       </c>
     </row>
     <row r="4">
@@ -2706,2847 +2706,2847 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.003161675529554486</v>
+        <v>0.2543430924415588</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1033695787191391</v>
+        <v>1.649117588996887</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002179569564759731</v>
+        <v>0.2158491015434265</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07066870480775833</v>
+        <v>1.107298851013184</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02594050392508507</v>
+        <v>0.07357164472341537</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00122056866530329</v>
+        <v>0.4453724920749664</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006589429453015327</v>
+        <v>0.1609509438276291</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004765575286000967</v>
+        <v>0.09451885521411896</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01057025231420994</v>
+        <v>0.004796195775270462</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01120646484196186</v>
+        <v>0.1587597280740738</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09276441484689713</v>
+        <v>1.221094846725464</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01024879235774279</v>
+        <v>0.5100435018539429</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05233302712440491</v>
+        <v>1.580982565879822</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02265487611293793</v>
+        <v>0.1793341636657715</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01115163415670395</v>
+        <v>0.1960491985082626</v>
       </c>
       <c r="P5" t="n">
-        <v>0.002945380751043558</v>
+        <v>0.05594494938850403</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02101469971239567</v>
+        <v>0.2122363746166229</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001884883735328913</v>
+        <v>0.3457868695259094</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01245849579572678</v>
+        <v>0.249542623758316</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01937250792980194</v>
+        <v>0.09203308075666428</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00956778135150671</v>
+        <v>0.05193247646093369</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005745989270508289</v>
+        <v>0.2262234687805176</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002655812539160252</v>
+        <v>0.04844899475574493</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01016640849411488</v>
+        <v>0.5399923324584961</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005771452561020851</v>
+        <v>0.1316009014844894</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01160166785120964</v>
+        <v>0.1380938291549683</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01632296480238438</v>
+        <v>0.3668528199195862</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0006124619394540787</v>
+        <v>0.09925058484077454</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.008113125339150429</v>
+        <v>0.05305314809083939</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.005270660389214754</v>
+        <v>0.0630040168762207</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.00338962278328836</v>
+        <v>0.3832655549049377</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.00723566859960556</v>
+        <v>0.09215840697288513</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.003148527117446065</v>
+        <v>0.1245435178279877</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.01037810929119587</v>
+        <v>0.1162022724747658</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.007619594689458609</v>
+        <v>0.1870776861906052</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.01030819863080978</v>
+        <v>0.01486928574740887</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.002246048301458359</v>
+        <v>0.5031054019927979</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02312956750392914</v>
+        <v>0.5556099414825439</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.004488970618695021</v>
+        <v>0.01619159430265427</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.005255474708974361</v>
+        <v>0.08058221638202667</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.005930677987635136</v>
+        <v>0.5351866483688354</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.00947556272149086</v>
+        <v>0.215148001909256</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.01072775758802891</v>
+        <v>0.09319393336772919</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.003831950714811683</v>
+        <v>0.03661203756928444</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.01013562083244324</v>
+        <v>0.2129513919353485</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.01396564766764641</v>
+        <v>0.4201916456222534</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.06187464669346809</v>
+        <v>0.7528466582298279</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.007916492410004139</v>
+        <v>0.1668269634246826</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.01531154382973909</v>
+        <v>0.4261931777000427</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.002820408903062344</v>
+        <v>0.324771523475647</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.0007310594664886594</v>
+        <v>0.04767066240310669</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.003442561253905296</v>
+        <v>0.01964210905134678</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.01905283704400063</v>
+        <v>0.2530926167964935</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.006952922325581312</v>
+        <v>0.1509441584348679</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0014058374799788</v>
+        <v>0.3258463144302368</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0187862291932106</v>
+        <v>0.5716100335121155</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.01123504061251879</v>
+        <v>0.1932992935180664</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.01569142937660217</v>
+        <v>0.1118657514452934</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.03203318268060684</v>
+        <v>0.2333915829658508</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.01040379237383604</v>
+        <v>0.5225347280502319</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.77954968623817e-05</v>
+        <v>0.01467931270599365</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0147238215431571</v>
+        <v>0.06452988088130951</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.004862784408032894</v>
+        <v>0.3128818571567535</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.01366537809371948</v>
+        <v>0.4707333743572235</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.006552122533321381</v>
+        <v>0.3648998737335205</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.003353512845933437</v>
+        <v>0.003204495180398226</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.004711759276688099</v>
+        <v>0.07872169464826584</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01286816503852606</v>
+        <v>0.01703865081071854</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.009784379974007607</v>
+        <v>0.2566612064838409</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.006454202812165022</v>
+        <v>0.03965121135115623</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.006433792412281036</v>
+        <v>0.1857959479093552</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.009567517787218094</v>
+        <v>0.06557979434728622</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.01388205774128437</v>
+        <v>0.40089350938797</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.03508659824728966</v>
+        <v>0.4334172904491425</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0001225282903760672</v>
+        <v>0.09199677407741547</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.009475285187363625</v>
+        <v>0.464451014995575</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.01088201347738504</v>
+        <v>0.09808292984962463</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.007919339463114738</v>
+        <v>0.3080132901668549</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.000272943580057472</v>
+        <v>0.06489818543195724</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.001636487897485495</v>
+        <v>0.1934166252613068</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0142235578969121</v>
+        <v>0.195706307888031</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.001080596353858709</v>
+        <v>0.3982688784599304</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.01806394383311272</v>
+        <v>0.4269540905952454</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.005294242408126593</v>
+        <v>0.1189045459032059</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01318417396396399</v>
+        <v>0.4023016095161438</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.003106301184743643</v>
+        <v>0.04954539611935616</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.001779939862899482</v>
+        <v>0.09874621033668518</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.006411860696971416</v>
+        <v>0.04206822440028191</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.002329582115635276</v>
+        <v>0.02586623467504978</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.005318771582096815</v>
+        <v>0.04375622421503067</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.01251843385398388</v>
+        <v>0.131738692522049</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.007238134276121855</v>
+        <v>0.3672675490379333</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.003029496176168323</v>
+        <v>0.3593664169311523</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.00927305780351162</v>
+        <v>0.2704043090343475</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.01360472477972507</v>
+        <v>0.2579070031642914</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.01264345832169056</v>
+        <v>0.2446183115243912</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.02448731474578381</v>
+        <v>0.03700217604637146</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.01223825197666883</v>
+        <v>0.2148105949163437</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.001205708016641438</v>
+        <v>0.3645627200603485</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.002731188200414181</v>
+        <v>0.3678234219551086</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.01745009049773216</v>
+        <v>0.3594465255737305</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.005989864002913237</v>
+        <v>0.1586264073848724</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.01595326513051987</v>
+        <v>0.3679407238960266</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.002061127917841077</v>
+        <v>0.01462532114237547</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.005523236002773046</v>
+        <v>0.05829057097434998</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.008213791996240616</v>
+        <v>0.02130314335227013</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0003935792483389378</v>
+        <v>0.03656551986932755</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.003016972681507468</v>
+        <v>0.01656583696603775</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.01159120630472898</v>
+        <v>0.04565465450286865</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.03047464787960052</v>
+        <v>0.4126983880996704</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.008099763654172421</v>
+        <v>0.2790379226207733</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.03840364888310432</v>
+        <v>0.08078877627849579</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.005633946508169174</v>
+        <v>0.0422346293926239</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.004020626656711102</v>
+        <v>0.2297536432743073</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.005294262431561947</v>
+        <v>0.06439658999443054</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.01075460389256477</v>
+        <v>0.4810033440589905</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.003165809670463204</v>
+        <v>0.08882934600114822</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.002632913645356894</v>
+        <v>0.02616030722856522</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.009525160305202007</v>
+        <v>0.2116808295249939</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.003218275727704167</v>
+        <v>0.03517577052116394</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.002619479782879353</v>
+        <v>0.2432767748832703</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.00530973169952631</v>
+        <v>0.08006724715232849</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.00843487586826086</v>
+        <v>0.05555684864521027</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0005962452851235867</v>
+        <v>0.2366274893283844</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0005329553969204426</v>
+        <v>0.06767913699150085</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.01545628812164068</v>
+        <v>0.4220473170280457</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.006724338978528976</v>
+        <v>0.02872490882873535</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01190209854394197</v>
+        <v>0.01407365873456001</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.008993301540613174</v>
+        <v>0.09988339245319366</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.01388094946742058</v>
+        <v>0.364489734172821</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.002977107418701053</v>
+        <v>0.2791152894496918</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.008584000170230865</v>
+        <v>0.299439400434494</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0008931608172133565</v>
+        <v>0.1628742665052414</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.004200730938464403</v>
+        <v>0.2189513593912125</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.004468748811632395</v>
+        <v>0.3315625786781311</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.006923648063093424</v>
+        <v>0.5635074973106384</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0167245976626873</v>
+        <v>0.2728577852249146</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.004803148098289967</v>
+        <v>0.002029132097959518</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.006038171239197254</v>
+        <v>0.2578815221786499</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.009372148662805557</v>
+        <v>0.0649338886141777</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.001095196232199669</v>
+        <v>0.03110380657017231</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.001136571867391467</v>
+        <v>0.005664549767971039</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.004831414669752121</v>
+        <v>0.04394876956939697</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.001398642431013286</v>
+        <v>0.07502730190753937</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.006655683740973473</v>
+        <v>0.4049489796161652</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.01674466952681541</v>
+        <v>0.1207948848605156</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.01473059505224228</v>
+        <v>0.1232362613081932</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.007001224439591169</v>
+        <v>0.02360157668590546</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.007515634875744581</v>
+        <v>0.1207176148891449</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.01192911434918642</v>
+        <v>0.07610075175762177</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.01025636121630669</v>
+        <v>0.01995739340782166</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.006897059269249439</v>
+        <v>0.2416395097970963</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.003855377668514848</v>
+        <v>0.2309688180685043</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.002141163451597095</v>
+        <v>0.4045543372631073</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.02037536166608334</v>
+        <v>0.3984056413173676</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.004955534357577562</v>
+        <v>0.1036046370863914</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.01456706784665585</v>
+        <v>0.4149137735366821</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.003176858881488442</v>
+        <v>0.08915233612060547</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.006860448513180017</v>
+        <v>0.0621771439909935</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.006885245442390442</v>
+        <v>0.01092564314603806</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0009298974182456732</v>
+        <v>0.03490941226482391</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.004725427832454443</v>
+        <v>0.006647204048931599</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.002404522150754929</v>
+        <v>0.2754466533660889</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.01318491157144308</v>
+        <v>0.2475057393312454</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.01465552486479282</v>
+        <v>0.3491977751255035</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.006303735077381134</v>
+        <v>0.1686866879463196</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.002432477194815874</v>
+        <v>0.3679110407829285</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0003206842520739883</v>
+        <v>0.2725798487663269</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.007345093879848719</v>
+        <v>0.03441031649708748</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.002375652780756354</v>
+        <v>0.2920141220092773</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.005843517370522022</v>
+        <v>0.04238995537161827</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0002189269289374352</v>
+        <v>0.1769203543663025</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.004927127622067928</v>
+        <v>0.5860608816146851</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0360114648938179</v>
+        <v>0.3231818675994873</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.003159698564559221</v>
+        <v>0.8690167665481567</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.008276743814349174</v>
+        <v>0.08400039374828339</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.001055974862538278</v>
+        <v>0.2501314878463745</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.002073637442663312</v>
+        <v>0.2414209991693497</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.007380328141152859</v>
+        <v>0.4806104898452759</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.002978529781103134</v>
+        <v>0.0614081583917141</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.007681007497012615</v>
+        <v>0.05112599581480026</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.002740539377555251</v>
+        <v>0.3530011177062988</v>
       </c>
       <c r="GA5" t="n">
-        <v>9.004687308333814e-05</v>
+        <v>0.1572313904762268</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.003357097040861845</v>
+        <v>0.1928358376026154</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.02098086848855019</v>
+        <v>0.4627408385276794</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.01344754360616207</v>
+        <v>0.07241635024547577</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.03054707124829292</v>
+        <v>0.7953809499740601</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.005482218228280544</v>
+        <v>0.1018113419413567</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.02056768350303173</v>
+        <v>0.2712423503398895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.02755915187299252</v>
+        <v>0.1872156709432602</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1825720965862274</v>
+        <v>0.7745529413223267</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01534488797187805</v>
+        <v>0.1697621643543243</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01888339966535568</v>
+        <v>0.1882971674203873</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03964833542704582</v>
+        <v>0.1356307119131088</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01964868418872356</v>
+        <v>0.5031487941741943</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009545081295073032</v>
+        <v>0.05591891705989838</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004523088689893484</v>
+        <v>0.1657633632421494</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005603714380413294</v>
+        <v>0.09940307587385178</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03608521074056625</v>
+        <v>0.1182586774230003</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1152602508664131</v>
+        <v>0.8864454030990601</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00315640470944345</v>
+        <v>0.2371498346328735</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00724700465798378</v>
+        <v>0.3409677147865295</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04073046147823334</v>
+        <v>0.02237364649772644</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01980654522776604</v>
+        <v>0.4067007005214691</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01492815464735031</v>
+        <v>0.04583291709423065</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04100879281759262</v>
+        <v>0.1292700320482254</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01027532201260328</v>
+        <v>0.08616349101066589</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002493524923920631</v>
+        <v>0.0444672629237175</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03499239310622215</v>
+        <v>0.06864762306213379</v>
       </c>
       <c r="U6" t="n">
-        <v>0.006109759211540222</v>
+        <v>0.01207204163074493</v>
       </c>
       <c r="V6" t="n">
-        <v>0.009122799150645733</v>
+        <v>0.09022388607263565</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02370420657098293</v>
+        <v>0.1156576722860336</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01131148636341095</v>
+        <v>0.1028806120157242</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0347636453807354</v>
+        <v>0.0338769257068634</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0243521835654974</v>
+        <v>0.07044803351163864</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0003794330114033073</v>
+        <v>0.1113582029938698</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02055914327502251</v>
+        <v>0.1945416182279587</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.04804573208093643</v>
+        <v>0.03052897751331329</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.01094694808125496</v>
+        <v>0.0005584314931184053</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.002751518972218037</v>
+        <v>0.2819387316703796</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.009509826079010963</v>
+        <v>0.151664212346077</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.01457562204450369</v>
+        <v>0.03012475185096264</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.008291309699416161</v>
+        <v>0.09718421846628189</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.004825019277632236</v>
+        <v>0.1698106229305267</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.01530923135578632</v>
+        <v>0.006169470492750406</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.03389168158173561</v>
+        <v>0.0589991956949234</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0169958770275116</v>
+        <v>0.1199798285961151</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.00301953312009573</v>
+        <v>0.03390975669026375</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.02196908742189407</v>
+        <v>0.06318652629852295</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.01761007308959961</v>
+        <v>0.03405052050948143</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.03693005070090294</v>
+        <v>0.06741400063037872</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.01057983376085758</v>
+        <v>0.08786675333976746</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.01551050506532192</v>
+        <v>0.0833827406167984</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.002879156498238444</v>
+        <v>0.07535898685455322</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.01039458066225052</v>
+        <v>0.1697220653295517</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.126827135682106</v>
+        <v>0.6358217000961304</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.00873788446187973</v>
+        <v>0.06681431829929352</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0277846697717905</v>
+        <v>0.1322124302387238</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.01864143833518028</v>
+        <v>0.2988159358501434</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.02238508872687817</v>
+        <v>0.2028226107358932</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.01361499167978764</v>
+        <v>0.007849905639886856</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.01274149958044291</v>
+        <v>0.03377823531627655</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.01235553063452244</v>
+        <v>0.03804409131407738</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.008559614419937134</v>
+        <v>0.09519942849874496</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.02854474261403084</v>
+        <v>0.03448275104165077</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.04472879320383072</v>
+        <v>0.1137455850839615</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.03428610041737556</v>
+        <v>0.1850524246692657</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.04179169982671738</v>
+        <v>0.1390565186738968</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.01899425499141216</v>
+        <v>0.1912708580493927</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.007376439869403839</v>
+        <v>0.05355263873934746</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.02772901952266693</v>
+        <v>0.1325625032186508</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.009293603710830212</v>
+        <v>0.09547595679759979</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.009636318311095238</v>
+        <v>0.04907769337296486</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.05454234033823013</v>
+        <v>0.0848623663187027</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0106284786015749</v>
+        <v>0.06490488350391388</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.02023961767554283</v>
+        <v>0.09461160004138947</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0405789241194725</v>
+        <v>0.01488129328936338</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.02551943250000477</v>
+        <v>0.02280760928988457</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.02689831703901291</v>
+        <v>0.2104993164539337</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.01831620931625366</v>
+        <v>0.01711144112050533</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.006566463969647884</v>
+        <v>0.05134616419672966</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.005019883625209332</v>
+        <v>0.05224078893661499</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.07002858072519302</v>
+        <v>0.2498707473278046</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0335068553686142</v>
+        <v>0.07179829478263855</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.02102941833436489</v>
+        <v>0.08804096281528473</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.01642685942351818</v>
+        <v>0.1161299198865891</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0006872075027786195</v>
+        <v>0.22628453373909</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.02377711795270443</v>
+        <v>0.03639283776283264</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.001295865513384342</v>
+        <v>0.03006780706346035</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0005707418895326555</v>
+        <v>0.04562358185648918</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.0008902410045266151</v>
+        <v>0.02519817650318146</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.02945854514837265</v>
+        <v>0.2193911075592041</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.003492885269224644</v>
+        <v>0.07856067270040512</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.009743189439177513</v>
+        <v>0.04590571671724319</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.002243987983092666</v>
+        <v>0.006799204275012016</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.001519521349109709</v>
+        <v>0.1049050986766815</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.002037323080003262</v>
+        <v>0.04068706929683685</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.003984345123171806</v>
+        <v>0.05224688723683357</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0001007480750558898</v>
+        <v>0.04099183902144432</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.04177962243556976</v>
+        <v>0.07308030128479004</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.02597523108124733</v>
+        <v>0.1028544455766678</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.01667744852602482</v>
+        <v>0.1693317592144012</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.01047714985907078</v>
+        <v>0.2638694941997528</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.005610718857496977</v>
+        <v>0.1782367676496506</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.05400028824806213</v>
+        <v>0.1663385480642319</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.02588003873825073</v>
+        <v>0.0275285467505455</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.01953507587313652</v>
+        <v>0.06653764098882675</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.005528089124709368</v>
+        <v>0.02505995333194733</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0006952465046197176</v>
+        <v>0.06200993806123734</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.02576448768377304</v>
+        <v>0.2106378972530365</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.01067520957440138</v>
+        <v>0.07240325957536697</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.01482000388205051</v>
+        <v>0.05383897200226784</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.003944212570786476</v>
+        <v>0.009634005837142467</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.004137339536100626</v>
+        <v>0.1207474246621132</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.001383704715408385</v>
+        <v>0.02641881257295609</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.002766667632386088</v>
+        <v>0.04647395387291908</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.002088452223688364</v>
+        <v>0.0333416722714901</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.02007362991571426</v>
+        <v>0.1235703229904175</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.06946311146020889</v>
+        <v>0.1016254723072052</v>
       </c>
       <c r="DG6" t="n">
-        <v>7.585948333144188e-05</v>
+        <v>0.0176013819873333</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.02232733182609081</v>
+        <v>0.0644504725933075</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.04179443046450615</v>
+        <v>0.1637200266122818</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.003056278685107827</v>
+        <v>0.2258657068014145</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.04482371732592583</v>
+        <v>0.04259262979030609</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.003571299836039543</v>
+        <v>0.02190489135682583</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.008788913488388062</v>
+        <v>0.1006025746464729</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.004831313155591488</v>
+        <v>0.09175936132669449</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.02274788729846478</v>
+        <v>0.04850855469703674</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.005821545142680407</v>
+        <v>0.07414159923791885</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.03668812662363052</v>
+        <v>0.01528772804886103</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0565275214612484</v>
+        <v>0.1356452405452728</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.00403312686830759</v>
+        <v>0.03602315112948418</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.001032589003443718</v>
+        <v>0.0395486056804657</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.008896623738110065</v>
+        <v>0.1019568294286728</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.003442163579165936</v>
+        <v>0.01286739762872458</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.000804916606284678</v>
+        <v>0.04669212177395821</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0185355469584465</v>
+        <v>0.02657093852758408</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.02596642822027206</v>
+        <v>0.1034005731344223</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.01017055660486221</v>
+        <v>0.1378849595785141</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0216534323990345</v>
+        <v>0.05860034748911858</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.002509932033717632</v>
+        <v>0.05740059167146683</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.01305597368627787</v>
+        <v>0.01105590630322695</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.02887331508100033</v>
+        <v>0.09718295931816101</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0005555886309593916</v>
+        <v>0.07850760221481323</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0153049835935235</v>
+        <v>0.002315466292202473</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.01464078016579151</v>
+        <v>0.1271194815635681</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.005946624092757702</v>
+        <v>0.002356342971324921</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.004381778184324503</v>
+        <v>0.0439806655049324</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.005706595722585917</v>
+        <v>0.04884854331612587</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.002026290399953723</v>
+        <v>0.06039104983210564</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.00438370555639267</v>
+        <v>0.03525988757610321</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.01119083538651466</v>
+        <v>0.01763163879513741</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.003274454735219479</v>
+        <v>0.0133072966709733</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.00850088894367218</v>
+        <v>0.04804461449384689</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.02738575264811516</v>
+        <v>0.1339434385299683</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0134749747812748</v>
+        <v>0.1026701703667641</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0334574282169342</v>
+        <v>0.007851205766201019</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.02205770835280418</v>
+        <v>0.07608018815517426</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.02051084488630295</v>
+        <v>0.09946965426206589</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.01579962857067585</v>
+        <v>0.02718625776469707</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.02117986232042313</v>
+        <v>0.0360168069601059</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.007211508695036173</v>
+        <v>0.01359121222048998</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.001914981286972761</v>
+        <v>0.03572474792599678</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.02407851070165634</v>
+        <v>0.2403097599744797</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.005988559685647488</v>
+        <v>0.06626157462596893</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.007100109942257404</v>
+        <v>0.06059163063764572</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.006625997368246317</v>
+        <v>0.04996925964951515</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.006284592673182487</v>
+        <v>0.1047857031226158</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.001561825280077755</v>
+        <v>0.04612826183438301</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.0007402982446365058</v>
+        <v>0.0521913543343544</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.003455021884292364</v>
+        <v>0.01599674113094807</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.00659866351634264</v>
+        <v>0.01489117834717035</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.005135721527040005</v>
+        <v>0.2303756773471832</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.01551816239953041</v>
+        <v>0.109981469810009</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.01139658596366644</v>
+        <v>0.03594972193241119</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.05403813347220421</v>
+        <v>0.1591189652681351</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01651955023407936</v>
+        <v>0.1522030234336853</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.008333930745720863</v>
+        <v>0.08693982660770416</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0235104151070118</v>
+        <v>0.09222736209630966</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.01038746722042561</v>
+        <v>0.1219028308987617</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.01285198889672756</v>
+        <v>0.0206486415117979</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.004369005560874939</v>
+        <v>0.1586239784955978</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.03257326781749725</v>
+        <v>0.1284135282039642</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.006749986670911312</v>
+        <v>0.2381622642278671</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.02186372689902782</v>
+        <v>0.01789847761392593</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.009426925331354141</v>
+        <v>0.09564705938100815</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.010914146900177</v>
+        <v>0.007895104587078094</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.006901874672621489</v>
+        <v>0.01010111905634403</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.004993064794689417</v>
+        <v>0.02512821182608604</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.03455073013901711</v>
+        <v>0.1112217754125595</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.008356251753866673</v>
+        <v>0.06041064113378525</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.01989794708788395</v>
+        <v>0.2515263259410858</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0158094335347414</v>
+        <v>0.008776630274951458</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.05332154780626297</v>
+        <v>0.1680903732776642</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.02959108352661133</v>
+        <v>0.1392212808132172</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.02329366095364094</v>
+        <v>0.05428987368941307</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.01928458921611309</v>
+        <v>0.05397512763738632</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.004269254859536886</v>
+        <v>0.04416533559560776</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.01574148423969746</v>
+        <v>0.1500957459211349</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2227109968662262</v>
+        <v>0.8567953109741211</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04445771872997284</v>
+        <v>0.1496734321117401</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3499568700790405</v>
+        <v>0.7608267664909363</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07997538149356842</v>
+        <v>0.1125992834568024</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08309376984834671</v>
+        <v>0.2640400528907776</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04902117326855659</v>
+        <v>0.3855392336845398</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0444304421544075</v>
+        <v>0.1245025843381882</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06223256140947342</v>
+        <v>0.0923321545124054</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06666669994592667</v>
+        <v>0.1245455294847488</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1987596303224564</v>
+        <v>0.7490657567977905</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0323965921998024</v>
+        <v>0.2556168138980865</v>
       </c>
       <c r="M7" t="n">
-        <v>0.266590029001236</v>
+        <v>1.08754563331604</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005984233692288399</v>
+        <v>0.237673819065094</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07784364372491837</v>
+        <v>0.01479234546422958</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03020785562694073</v>
+        <v>0.3023222684860229</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0744229257106781</v>
+        <v>0.1350893974304199</v>
       </c>
       <c r="R7" t="n">
-        <v>0.07386145740747452</v>
+        <v>0.03618890047073364</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003115398809313774</v>
+        <v>0.07486528903245926</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03979215025901794</v>
+        <v>0.04919616878032684</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03021175600588322</v>
+        <v>0.03066547960042953</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1212240532040596</v>
+        <v>0.04517282173037529</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01044232770800591</v>
+        <v>0.05032327026128769</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06987033039331436</v>
+        <v>0.2520944178104401</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01258928701281548</v>
+        <v>0.0696851834654808</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01437461748719215</v>
+        <v>0.083208829164505</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00685828784480691</v>
+        <v>0.1875098347663879</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.008568044751882553</v>
+        <v>0.114720918238163</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.02785663492977619</v>
+        <v>0.07642462849617004</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01522601675242186</v>
+        <v>0.07546435296535492</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.04216241836547852</v>
+        <v>0.07552608847618103</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.005435789003968239</v>
+        <v>0.1226111650466919</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.02534516900777817</v>
+        <v>0.03373802825808525</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0006239525973796844</v>
+        <v>0.02675729244947433</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01639747619628906</v>
+        <v>0.1413443833589554</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.07510411739349365</v>
+        <v>0.02742923609912395</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.005202293395996094</v>
+        <v>0.1592440456151962</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.035910964012146</v>
+        <v>0.2901631891727448</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.03007315844297409</v>
+        <v>0.01368349976837635</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.01326649822294712</v>
+        <v>0.09063509106636047</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0174855925142765</v>
+        <v>0.334921270608902</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.01914051733911037</v>
+        <v>0.1701117753982544</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.519079372286797e-05</v>
+        <v>0.005967170000076294</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.02349478751420975</v>
+        <v>0.08233007788658142</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.05228390917181969</v>
+        <v>0.06537093967199326</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.02001497335731983</v>
+        <v>0.1693125069141388</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.04812120273709297</v>
+        <v>0.5577694177627563</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0372067503631115</v>
+        <v>0.1217491775751114</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1517287045717239</v>
+        <v>0.4367505311965942</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.08514851331710815</v>
+        <v>0.2826879322528839</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.03183760493993759</v>
+        <v>0.03884512558579445</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.002664800733327866</v>
+        <v>0.05668460950255394</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.02402563393115997</v>
+        <v>0.03257264196872711</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.07346607744693756</v>
+        <v>0.002919569611549377</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0536741130053997</v>
+        <v>0.1384088695049286</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.07966969162225723</v>
+        <v>0.04628972709178925</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.06921958178281784</v>
+        <v>0.1566476672887802</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.1091634929180145</v>
+        <v>0.1269797086715698</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.008326029404997826</v>
+        <v>0.06341467052698135</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0397672988474369</v>
+        <v>0.1937820315361023</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.02254095114767551</v>
+        <v>0.187332808971405</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.08631338179111481</v>
+        <v>0.05801346153020859</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.04552192986011505</v>
+        <v>0.1965740472078323</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.02427484467625618</v>
+        <v>0.07679478079080582</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03682712838053703</v>
+        <v>0.1474592983722687</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.04679456353187561</v>
+        <v>0.04395031183958054</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.009271852672100067</v>
+        <v>0.02532530575990677</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.01732894219458103</v>
+        <v>0.05436115711927414</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.02414608933031559</v>
+        <v>0.02741963602602482</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.007554812356829643</v>
+        <v>0.02623138017952442</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.02735469862818718</v>
+        <v>0.1411241292953491</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.005968140903860331</v>
+        <v>0.08135879039764404</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.06979877501726151</v>
+        <v>0.1049153655767441</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.04108454659581184</v>
+        <v>0.3332030773162842</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.04789527878165245</v>
+        <v>0.008748491294682026</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.09036656469106674</v>
+        <v>0.4550319910049438</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0254815611988306</v>
+        <v>0.0451490506529808</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.004826955031603575</v>
+        <v>0.130875825881958</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0008776914328336716</v>
+        <v>0.02976149693131447</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.01970692351460457</v>
+        <v>0.04540616646409035</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.06020191311836243</v>
+        <v>0.1390243172645569</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0171554870903492</v>
+        <v>0.07655356824398041</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.01776230148971081</v>
+        <v>0.255229651927948</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.03061583824455738</v>
+        <v>0.06759160757064819</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0681125670671463</v>
+        <v>0.2921237349510193</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0171052273362875</v>
+        <v>0.03776418045163155</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.01308627426624298</v>
+        <v>0.009216690436005592</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.007131094112992287</v>
+        <v>0.009208951145410538</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0007485932437703013</v>
+        <v>0.01222373079508543</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.02480482868850231</v>
+        <v>0.05442492663860321</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.005624604877084494</v>
+        <v>0.00922040268778801</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.06764363497495651</v>
+        <v>0.1522850692272186</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.01756161451339722</v>
+        <v>0.1467919647693634</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.004507751669734716</v>
+        <v>0.3695693016052246</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0141578447073698</v>
+        <v>0.02432828024029732</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.01553351152688265</v>
+        <v>0.03416663408279419</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.07149024307727814</v>
+        <v>0.005892939865589142</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.001369130332022905</v>
+        <v>0.01084984838962555</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.006677780300378799</v>
+        <v>0.1812240481376648</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.02068613842129707</v>
+        <v>0.07439034432172775</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.02679215371608734</v>
+        <v>0.240998238325119</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.03168622031807899</v>
+        <v>0.07415218651294708</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.06295933574438095</v>
+        <v>0.2821709513664246</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.02450700104236603</v>
+        <v>0.00463876174762845</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.01107378862798214</v>
+        <v>0.000314599834382534</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.01914197765290737</v>
+        <v>0.01351461932063103</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.009269046597182751</v>
+        <v>0.002984672319144011</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.01219360902905464</v>
+        <v>0.07187473773956299</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.001882098615169525</v>
+        <v>0.01782973855733871</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.08359323441982269</v>
+        <v>0.3071565330028534</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0002932832576334476</v>
+        <v>0.02722273766994476</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.1204749196767807</v>
+        <v>0.1140682175755501</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.06577607989311218</v>
+        <v>0.06198579072952271</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.08874616026878357</v>
+        <v>0.2669260799884796</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.05595738813281059</v>
+        <v>0.1144966334104538</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.05884099006652832</v>
+        <v>0.3973711729049683</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.0619935467839241</v>
+        <v>0.01441110670566559</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0148712545633316</v>
+        <v>0.01980667561292648</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.003873853478580713</v>
+        <v>0.1301914751529694</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.01191472355276346</v>
+        <v>0.03382477909326553</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.05140358209609985</v>
+        <v>0.1412782520055771</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.02963202446699142</v>
+        <v>0.01189311780035496</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.01090471353381872</v>
+        <v>0.0235876739025116</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.01410000957548618</v>
+        <v>0.1229967623949051</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.03381410986185074</v>
+        <v>0.09896096587181091</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.04736814647912979</v>
+        <v>0.3147839605808258</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.01616588607430458</v>
+        <v>0.0126174446195364</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.00442492077127099</v>
+        <v>0.003178983926773071</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.009855327196419239</v>
+        <v>0.04139205440878868</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.03876035660505295</v>
+        <v>0.1076250970363617</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.02284896932542324</v>
+        <v>0.03321044892072678</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.01987172849476337</v>
+        <v>0.03319422900676727</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.007897600531578064</v>
+        <v>0.08639951795339584</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.02803926914930344</v>
+        <v>0.1996016502380371</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.01032765489071608</v>
+        <v>0.3075233995914459</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.002667720895260572</v>
+        <v>0.08274374902248383</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.03004501387476921</v>
+        <v>0.2331798374652863</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.02991179004311562</v>
+        <v>0.03079502284526825</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.01902839541435242</v>
+        <v>0.2566042244434357</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.001068117097020149</v>
+        <v>0.08921444416046143</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.03674055263400078</v>
+        <v>0.02981185354292393</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.01244701445102692</v>
+        <v>0.02396884560585022</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.01402581483125687</v>
+        <v>0.01665700972080231</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.01647920906543732</v>
+        <v>0.0120664332062006</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0595150887966156</v>
+        <v>0.1082945987582207</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.01413779053837061</v>
+        <v>0.1078038886189461</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.03500551357865334</v>
+        <v>0.01299544703215361</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.03773754835128784</v>
+        <v>0.1574404686689377</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.01295421738177538</v>
+        <v>0.006936083547770977</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.05368126556277275</v>
+        <v>0.04460316896438599</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.04303243383765221</v>
+        <v>0.01187153905630112</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.06847956776618958</v>
+        <v>0.1152133345603943</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.01546513009816408</v>
+        <v>0.142584353685379</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.01664072275161743</v>
+        <v>0.07624534517526627</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.01649820990860462</v>
+        <v>0.2688041031360626</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.02906943298876286</v>
+        <v>0.05931892991065979</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.06747785955667496</v>
+        <v>0.3292956054210663</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.01126998756080866</v>
+        <v>0.02214411459863186</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.008634838275611401</v>
+        <v>0.01152046397328377</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.01548742037266493</v>
+        <v>0.0181436762213707</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.01287421863526106</v>
+        <v>0.02998713962733746</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.02628712728619576</v>
+        <v>0.07482318580150604</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.05717411637306213</v>
+        <v>0.05880481749773026</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.02052943408489227</v>
+        <v>0.1742108762264252</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.02271570824086666</v>
+        <v>0.2329406440258026</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.009056409820914268</v>
+        <v>0.1579704284667969</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.03783991932868958</v>
+        <v>0.1795690804719925</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.01012547314167023</v>
+        <v>0.07078442722558975</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.001886941492557526</v>
+        <v>0.0127548985183239</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.03729858994483948</v>
+        <v>0.029154933989048</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.02423261292278767</v>
+        <v>0.1551910787820816</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.01700423657894135</v>
+        <v>0.05209315568208694</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.02368604764342308</v>
+        <v>0.3653566837310791</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.04977728798985481</v>
+        <v>0.1044162660837173</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.006445123814046383</v>
+        <v>0.5517603158950806</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.03663047030568123</v>
+        <v>0.05405666679143906</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.04613678529858589</v>
+        <v>0.06563892960548401</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.04935716465115547</v>
+        <v>0.04753692820668221</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.01724418625235558</v>
+        <v>0.07213539630174637</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.007499080616980791</v>
+        <v>0.2143490314483643</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.004819395020604134</v>
+        <v>0.1039809733629227</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.04888434708118439</v>
+        <v>0.1619680970907211</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.006675674580037594</v>
+        <v>0.1070881560444832</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0126816388219595</v>
+        <v>0.1764825731515884</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.02589413337409496</v>
+        <v>0.3477909564971924</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.02267803996801376</v>
+        <v>0.03148970007896423</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.1194637566804886</v>
+        <v>0.292367547750473</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.05051857978105545</v>
+        <v>0.1294177919626236</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.01923797279596329</v>
+        <v>0.01137144863605499</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6.985816725091354e-08</v>
+        <v>0.03874216601252556</v>
       </c>
       <c r="B8" t="n">
-        <v>5.180320172826214e-09</v>
+        <v>0.6895706653594971</v>
       </c>
       <c r="C8" t="n">
-        <v>4.248877161217024e-08</v>
+        <v>0.05044268071651459</v>
       </c>
       <c r="D8" t="n">
-        <v>7.906120202960665e-08</v>
+        <v>0.6631903648376465</v>
       </c>
       <c r="E8" t="n">
-        <v>1.925897663568321e-09</v>
+        <v>0.04012633860111237</v>
       </c>
       <c r="F8" t="n">
-        <v>3.017159855289719e-08</v>
+        <v>0.4527179896831512</v>
       </c>
       <c r="G8" t="n">
-        <v>4.430673605781976e-10</v>
+        <v>0.2579244077205658</v>
       </c>
       <c r="H8" t="n">
-        <v>2.359092654558026e-08</v>
+        <v>0.3041145503520966</v>
       </c>
       <c r="I8" t="n">
-        <v>3.268592863037156e-08</v>
+        <v>0.01845698431134224</v>
       </c>
       <c r="J8" t="n">
-        <v>4.031862133047071e-08</v>
+        <v>0.07955982536077499</v>
       </c>
       <c r="K8" t="n">
-        <v>4.663398200932534e-08</v>
+        <v>0.6324411630630493</v>
       </c>
       <c r="L8" t="n">
-        <v>3.61447547447824e-08</v>
+        <v>0.1415912657976151</v>
       </c>
       <c r="M8" t="n">
-        <v>1.033842522701889e-08</v>
+        <v>0.8207159042358398</v>
       </c>
       <c r="N8" t="n">
-        <v>2.729099080056585e-08</v>
+        <v>0.0469273179769516</v>
       </c>
       <c r="O8" t="n">
-        <v>8.131597439842153e-08</v>
+        <v>0.482240617275238</v>
       </c>
       <c r="P8" t="n">
-        <v>7.068117202635449e-09</v>
+        <v>0.2813540101051331</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.30330571784998e-08</v>
+        <v>0.1536960601806641</v>
       </c>
       <c r="R8" t="n">
-        <v>5.367879474249548e-09</v>
+        <v>0.01557451114058495</v>
       </c>
       <c r="S8" t="n">
-        <v>1.698689899853889e-08</v>
+        <v>0.08966904878616333</v>
       </c>
       <c r="T8" t="n">
-        <v>1.350858536142141e-08</v>
+        <v>0.03012686409056187</v>
       </c>
       <c r="U8" t="n">
-        <v>1.780882818991358e-08</v>
+        <v>0.05747545510530472</v>
       </c>
       <c r="V8" t="n">
-        <v>2.718112845911946e-08</v>
+        <v>0.02888301759958267</v>
       </c>
       <c r="W8" t="n">
-        <v>9.099996844952329e-08</v>
+        <v>0.1072142198681831</v>
       </c>
       <c r="X8" t="n">
-        <v>2.501079343630863e-09</v>
+        <v>0.06739664077758789</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.994761854642093e-08</v>
+        <v>0.0588720478117466</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.13669126228433e-08</v>
+        <v>0.09182476252317429</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.078365023474362e-08</v>
+        <v>0.02679755166172981</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.906306756893628e-08</v>
+        <v>0.01209937036037445</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.488612610955897e-08</v>
+        <v>0.2165833711624146</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.781310565718286e-08</v>
+        <v>0.09559357166290283</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.617682071104355e-08</v>
+        <v>0.0026099793612957</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.120358383843723e-08</v>
+        <v>0.1638984382152557</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.455822022464417e-08</v>
+        <v>0.07284604012966156</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.099879464230071e-08</v>
+        <v>0.008965965360403061</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.946983729794738e-08</v>
+        <v>0.1032435446977615</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.161642775888595e-08</v>
+        <v>0.05846315249800682</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.847273445321207e-10</v>
+        <v>0.1202581897377968</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.594599557426136e-08</v>
+        <v>0.103587344288826</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.814682969505157e-08</v>
+        <v>0.1176986321806908</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.251199937575166e-08</v>
+        <v>0.2712091505527496</v>
       </c>
       <c r="AO8" t="n">
-        <v>3.04573966047883e-08</v>
+        <v>0.1021339371800423</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.023316429486613e-09</v>
+        <v>0.06324098259210587</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.394732151993594e-08</v>
+        <v>0.006168916821479797</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.664370685716676e-08</v>
+        <v>0.03398331254720688</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.437913757650904e-09</v>
+        <v>0.004448088817298412</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.412998873462357e-08</v>
+        <v>0.02812035381793976</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.954170514295583e-08</v>
+        <v>0.4074555933475494</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.206878774695497e-08</v>
+        <v>0.02087239176034927</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.790558788021372e-08</v>
+        <v>0.4189072847366333</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.284266915035914e-08</v>
+        <v>0.2835679352283478</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.952831223979047e-08</v>
+        <v>0.1827507019042969</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.117592311558838e-08</v>
+        <v>0.0008329837583005428</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.005822891642083e-08</v>
+        <v>0.00175328878685832</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.207917943446546e-08</v>
+        <v>0.08580213785171509</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.284571986090668e-08</v>
+        <v>0.1557177156209946</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.822604194818723e-08</v>
+        <v>0.1024932563304901</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.521020713355028e-08</v>
+        <v>0.08198487758636475</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.032721191369546e-08</v>
+        <v>0.08365152031183243</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.601854731665298e-08</v>
+        <v>0.205317884683609</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.295264860980751e-08</v>
+        <v>0.1161996126174927</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.997780157443231e-08</v>
+        <v>0.163502961397171</v>
       </c>
       <c r="BJ8" t="n">
-        <v>5.178385364956739e-08</v>
+        <v>0.2337001413106918</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.791649850702015e-08</v>
+        <v>0.1133748814463615</v>
       </c>
       <c r="BL8" t="n">
-        <v>2.30519923150041e-08</v>
+        <v>0.0717131495475769</v>
       </c>
       <c r="BM8" t="n">
-        <v>3.382852753475163e-08</v>
+        <v>0.02854888699948788</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.31107826817356e-08</v>
+        <v>0.05412615835666656</v>
       </c>
       <c r="BO8" t="n">
-        <v>2.714592817198991e-08</v>
+        <v>0.06664973497390747</v>
       </c>
       <c r="BP8" t="n">
-        <v>9.447735038747851e-09</v>
+        <v>0.09656223654747009</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.429956952847533e-08</v>
+        <v>0.01046251133084297</v>
       </c>
       <c r="BR8" t="n">
-        <v>3.961136751939875e-09</v>
+        <v>0.04329235851764679</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.330669885390989e-08</v>
+        <v>0.08963568508625031</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.860840949864723e-09</v>
+        <v>0.008856078609824181</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.894215794275624e-08</v>
+        <v>0.06502239406108856</v>
       </c>
       <c r="BV8" t="n">
-        <v>1.408291616655788e-08</v>
+        <v>0.09502924233675003</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.986868269909792e-08</v>
+        <v>0.04162980988621712</v>
       </c>
       <c r="BX8" t="n">
-        <v>3.462594433401023e-09</v>
+        <v>0.2872176766395569</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.278134398319253e-08</v>
+        <v>0.01325320545583963</v>
       </c>
       <c r="BZ8" t="n">
-        <v>5.060824204150549e-09</v>
+        <v>0.09424322843551636</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.58859351731644e-08</v>
+        <v>0.07182736694812775</v>
       </c>
       <c r="CB8" t="n">
-        <v>2.046661862209476e-08</v>
+        <v>0.05986576899886131</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.108791719024339e-08</v>
+        <v>0.02312581054866314</v>
       </c>
       <c r="CD8" t="n">
-        <v>1.30845343448982e-08</v>
+        <v>0.02018621563911438</v>
       </c>
       <c r="CE8" t="n">
-        <v>5.427833738025356e-10</v>
+        <v>0.1884474158287048</v>
       </c>
       <c r="CF8" t="n">
-        <v>9.736094597201372e-09</v>
+        <v>0.02516844496130943</v>
       </c>
       <c r="CG8" t="n">
-        <v>1.453425713116019e-10</v>
+        <v>0.2321667969226837</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.251251102729611e-08</v>
+        <v>0.01096588000655174</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.108339287014815e-08</v>
+        <v>0.07406897097826004</v>
       </c>
       <c r="CJ8" t="n">
-        <v>5.399363178781869e-09</v>
+        <v>0.004982316866517067</v>
       </c>
       <c r="CK8" t="n">
-        <v>6.286835940727542e-09</v>
+        <v>0.03963453322649002</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.888216694112543e-08</v>
+        <v>0.004228697158396244</v>
       </c>
       <c r="CM8" t="n">
-        <v>4.65782825642691e-08</v>
+        <v>0.1336713582277298</v>
       </c>
       <c r="CN8" t="n">
-        <v>5.609355646640779e-09</v>
+        <v>0.065694659948349</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.675765481934377e-08</v>
+        <v>0.1076194941997528</v>
       </c>
       <c r="CP8" t="n">
-        <v>5.545510362026107e-08</v>
+        <v>0.1748876869678497</v>
       </c>
       <c r="CQ8" t="n">
-        <v>6.104149008478998e-08</v>
+        <v>0.05732806771993637</v>
       </c>
       <c r="CR8" t="n">
-        <v>2.066470017325628e-08</v>
+        <v>0.04494835436344147</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.699943462720512e-08</v>
+        <v>0.01121022552251816</v>
       </c>
       <c r="CT8" t="n">
-        <v>4.849878010304565e-08</v>
+        <v>0.1593822687864304</v>
       </c>
       <c r="CU8" t="n">
-        <v>6.537478469681446e-08</v>
+        <v>0.0004471598658710718</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.006838701300694e-08</v>
+        <v>0.01244900934398174</v>
       </c>
       <c r="CW8" t="n">
-        <v>3.350929755896459e-09</v>
+        <v>0.1700654625892639</v>
       </c>
       <c r="CX8" t="n">
-        <v>2.236969498525809e-09</v>
+        <v>0.03177584707736969</v>
       </c>
       <c r="CY8" t="n">
-        <v>9.847045845390312e-09</v>
+        <v>0.2152418345212936</v>
       </c>
       <c r="CZ8" t="n">
-        <v>6.729278023698271e-09</v>
+        <v>0.01262030936777592</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.429030405120102e-08</v>
+        <v>0.08261941373348236</v>
       </c>
       <c r="DB8" t="n">
-        <v>6.095024485119893e-09</v>
+        <v>0.01665595918893814</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.444253605598078e-09</v>
+        <v>0.0478728823363781</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.636386492975817e-08</v>
+        <v>0.001060927635990083</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.261586390910452e-08</v>
+        <v>0.04618120566010475</v>
       </c>
       <c r="DF8" t="n">
-        <v>3.386854885434332e-08</v>
+        <v>0.25855952501297</v>
       </c>
       <c r="DG8" t="n">
-        <v>7.955259917480362e-08</v>
+        <v>0.2458036839962006</v>
       </c>
       <c r="DH8" t="n">
-        <v>9.923876120865316e-08</v>
+        <v>0.1183811873197556</v>
       </c>
       <c r="DI8" t="n">
-        <v>9.045281501585123e-08</v>
+        <v>0.1479177325963974</v>
       </c>
       <c r="DJ8" t="n">
-        <v>6.188887624603012e-08</v>
+        <v>0.2607186734676361</v>
       </c>
       <c r="DK8" t="n">
-        <v>2.336991711260339e-10</v>
+        <v>0.03909602016210556</v>
       </c>
       <c r="DL8" t="n">
-        <v>7.555524206281916e-08</v>
+        <v>0.2627499997615814</v>
       </c>
       <c r="DM8" t="n">
-        <v>2.497461792927425e-08</v>
+        <v>0.1144926175475121</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.194222765121822e-08</v>
+        <v>0.01673975400626659</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.919043223277185e-08</v>
+        <v>0.06357240676879883</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.298235958965506e-09</v>
+        <v>0.06207957863807678</v>
       </c>
       <c r="DQ8" t="n">
-        <v>2.052265024587996e-08</v>
+        <v>0.1854733526706696</v>
       </c>
       <c r="DR8" t="n">
-        <v>2.294515688561205e-08</v>
+        <v>0.02841569297015667</v>
       </c>
       <c r="DS8" t="n">
-        <v>1.254838721820306e-08</v>
+        <v>0.04928063601255417</v>
       </c>
       <c r="DT8" t="n">
-        <v>6.98503477281065e-09</v>
+        <v>0.1212612837553024</v>
       </c>
       <c r="DU8" t="n">
-        <v>5.594991581148179e-09</v>
+        <v>0.04205240309238434</v>
       </c>
       <c r="DV8" t="n">
-        <v>3.868085585168046e-08</v>
+        <v>0.1086905747652054</v>
       </c>
       <c r="DW8" t="n">
-        <v>5.175202488771902e-08</v>
+        <v>0.04139018058776855</v>
       </c>
       <c r="DX8" t="n">
-        <v>1.150537176641819e-08</v>
+        <v>0.1329375207424164</v>
       </c>
       <c r="DY8" t="n">
-        <v>5.766531074868908e-08</v>
+        <v>0.06354364007711411</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.46519123897815e-08</v>
+        <v>0.1785632222890854</v>
       </c>
       <c r="EA8" t="n">
-        <v>2.381837482801075e-08</v>
+        <v>0.05522433668375015</v>
       </c>
       <c r="EB8" t="n">
-        <v>2.197228621270142e-09</v>
+        <v>3.33692878484726e-05</v>
       </c>
       <c r="EC8" t="n">
-        <v>4.109129392304567e-08</v>
+        <v>0.0539737306535244</v>
       </c>
       <c r="ED8" t="n">
-        <v>1.927037018845112e-08</v>
+        <v>0.2724932134151459</v>
       </c>
       <c r="EE8" t="n">
-        <v>8.419525521219384e-09</v>
+        <v>0.2449453920125961</v>
       </c>
       <c r="EF8" t="n">
-        <v>5.99160543401922e-09</v>
+        <v>0.04931702837347984</v>
       </c>
       <c r="EG8" t="n">
-        <v>4.487664906349664e-09</v>
+        <v>0.1651308089494705</v>
       </c>
       <c r="EH8" t="n">
-        <v>3.092756628575444e-08</v>
+        <v>0.05133407190442085</v>
       </c>
       <c r="EI8" t="n">
-        <v>2.030901313787581e-08</v>
+        <v>0.1288219839334488</v>
       </c>
       <c r="EJ8" t="n">
-        <v>1.228515333906444e-08</v>
+        <v>0.1482934504747391</v>
       </c>
       <c r="EK8" t="n">
-        <v>1.676161431873879e-08</v>
+        <v>0.124689906835556</v>
       </c>
       <c r="EL8" t="n">
-        <v>7.335617890902313e-09</v>
+        <v>0.03634273260831833</v>
       </c>
       <c r="EM8" t="n">
-        <v>2.64645505509975e-09</v>
+        <v>0.002208102494478226</v>
       </c>
       <c r="EN8" t="n">
-        <v>6.939761654223275e-09</v>
+        <v>0.01600654050707817</v>
       </c>
       <c r="EO8" t="n">
-        <v>8.325088174387929e-09</v>
+        <v>0.05035838112235069</v>
       </c>
       <c r="EP8" t="n">
-        <v>2.929255060735159e-08</v>
+        <v>0.002245955169200897</v>
       </c>
       <c r="EQ8" t="n">
-        <v>3.229265033155571e-08</v>
+        <v>0.03489823266863823</v>
       </c>
       <c r="ER8" t="n">
-        <v>1.328209764395183e-09</v>
+        <v>0.05617620795965195</v>
       </c>
       <c r="ES8" t="n">
-        <v>1.619545031417147e-08</v>
+        <v>0.02338897436857224</v>
       </c>
       <c r="ET8" t="n">
-        <v>4.144411480666577e-09</v>
+        <v>0.004359573591500521</v>
       </c>
       <c r="EU8" t="n">
-        <v>3.912366608460616e-08</v>
+        <v>0.07423929870128632</v>
       </c>
       <c r="EV8" t="n">
-        <v>6.322948564729813e-08</v>
+        <v>0.1062702536582947</v>
       </c>
       <c r="EW8" t="n">
-        <v>1.660894000110602e-08</v>
+        <v>0.04789207503199577</v>
       </c>
       <c r="EX8" t="n">
-        <v>1.509955538381291e-08</v>
+        <v>0.02611132338643074</v>
       </c>
       <c r="EY8" t="n">
-        <v>5.545417458563406e-09</v>
+        <v>0.2013275176286697</v>
       </c>
       <c r="EZ8" t="n">
-        <v>1.978239794198089e-09</v>
+        <v>0.02599124796688557</v>
       </c>
       <c r="FA8" t="n">
-        <v>8.200029544269682e-10</v>
+        <v>0.2553099691867828</v>
       </c>
       <c r="FB8" t="n">
-        <v>1.108840397279209e-08</v>
+        <v>0.01483733486384153</v>
       </c>
       <c r="FC8" t="n">
-        <v>1.120435566548394e-08</v>
+        <v>0.06508777290582657</v>
       </c>
       <c r="FD8" t="n">
-        <v>4.271575093639512e-09</v>
+        <v>0.003212938085198402</v>
       </c>
       <c r="FE8" t="n">
-        <v>3.628218392393023e-09</v>
+        <v>0.07897508889436722</v>
       </c>
       <c r="FF8" t="n">
-        <v>1.403155547308188e-08</v>
+        <v>0.02329078316688538</v>
       </c>
       <c r="FG8" t="n">
-        <v>9.381965426769057e-09</v>
+        <v>0.08387930691242218</v>
       </c>
       <c r="FH8" t="n">
-        <v>2.631486140103334e-10</v>
+        <v>0.09341053664684296</v>
       </c>
       <c r="FI8" t="n">
-        <v>5.187153817587387e-08</v>
+        <v>0.03037671372294426</v>
       </c>
       <c r="FJ8" t="n">
-        <v>1.196078969201153e-08</v>
+        <v>0.1198208928108215</v>
       </c>
       <c r="FK8" t="n">
-        <v>1.052894038622298e-08</v>
+        <v>0.1870877295732498</v>
       </c>
       <c r="FL8" t="n">
-        <v>2.654333819407384e-08</v>
+        <v>0.05259804055094719</v>
       </c>
       <c r="FM8" t="n">
-        <v>1.641087266079921e-10</v>
+        <v>0.1048203930258751</v>
       </c>
       <c r="FN8" t="n">
-        <v>2.786616448702262e-08</v>
+        <v>0.1036892458796501</v>
       </c>
       <c r="FO8" t="n">
-        <v>2.124772535694319e-08</v>
+        <v>0.07572180777788162</v>
       </c>
       <c r="FP8" t="n">
-        <v>5.866122521069883e-08</v>
+        <v>0.1431514173746109</v>
       </c>
       <c r="FQ8" t="n">
-        <v>3.897232758731661e-09</v>
+        <v>0.3302048742771149</v>
       </c>
       <c r="FR8" t="n">
-        <v>5.091979460303264e-08</v>
+        <v>0.2719361186027527</v>
       </c>
       <c r="FS8" t="n">
-        <v>8.446495947111998e-09</v>
+        <v>0.1610198467969894</v>
       </c>
       <c r="FT8" t="n">
-        <v>1.76338632584816e-09</v>
+        <v>0.06146052107214928</v>
       </c>
       <c r="FU8" t="n">
-        <v>3.383187774375074e-08</v>
+        <v>0.1493579596281052</v>
       </c>
       <c r="FV8" t="n">
-        <v>7.35358227643701e-08</v>
+        <v>0.005429014563560486</v>
       </c>
       <c r="FW8" t="n">
-        <v>3.916129642789201e-09</v>
+        <v>0.01156935095787048</v>
       </c>
       <c r="FX8" t="n">
-        <v>1.047256414921094e-08</v>
+        <v>0.2091941684484482</v>
       </c>
       <c r="FY8" t="n">
-        <v>3.225790967675835e-09</v>
+        <v>0.1233052164316177</v>
       </c>
       <c r="FZ8" t="n">
-        <v>4.079585025351662e-08</v>
+        <v>0.01312274858355522</v>
       </c>
       <c r="GA8" t="n">
-        <v>4.274515319480088e-08</v>
+        <v>0.006493226159363985</v>
       </c>
       <c r="GB8" t="n">
-        <v>7.258270429133518e-09</v>
+        <v>0.1437418907880783</v>
       </c>
       <c r="GC8" t="n">
-        <v>4.230443195751832e-08</v>
+        <v>0.09124302119016647</v>
       </c>
       <c r="GD8" t="n">
-        <v>1.87242736870985e-08</v>
+        <v>0.02662492915987968</v>
       </c>
       <c r="GE8" t="n">
-        <v>2.762746831308505e-08</v>
+        <v>0.1467012912034988</v>
       </c>
       <c r="GF8" t="n">
-        <v>2.115345054676254e-08</v>
+        <v>0.06405638158321381</v>
       </c>
       <c r="GG8" t="n">
-        <v>3.90220691315335e-08</v>
+        <v>0.05981676653027534</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.047824227384808e-08</v>
+        <v>0.006225745193660259</v>
       </c>
       <c r="B9" t="n">
-        <v>1.663741144852793e-09</v>
+        <v>0.1206037700176239</v>
       </c>
       <c r="C9" t="n">
-        <v>9.920126053941658e-09</v>
+        <v>0.0004188418388366699</v>
       </c>
       <c r="D9" t="n">
-        <v>5.594851160140024e-08</v>
+        <v>0.1078503131866455</v>
       </c>
       <c r="E9" t="n">
-        <v>2.174269297938736e-08</v>
+        <v>0.04330795258283615</v>
       </c>
       <c r="F9" t="n">
-        <v>9.544049106580133e-08</v>
+        <v>0.09394853562116623</v>
       </c>
       <c r="G9" t="n">
-        <v>1.717461728389935e-08</v>
+        <v>0.04968014359474182</v>
       </c>
       <c r="H9" t="n">
-        <v>2.537552568071533e-08</v>
+        <v>0.0555744543671608</v>
       </c>
       <c r="I9" t="n">
-        <v>4.036076806102074e-09</v>
+        <v>0.01505497097969055</v>
       </c>
       <c r="J9" t="n">
-        <v>3.968763095940631e-09</v>
+        <v>0.02553916350007057</v>
       </c>
       <c r="K9" t="n">
-        <v>9.201828632399156e-09</v>
+        <v>0.112418070435524</v>
       </c>
       <c r="L9" t="n">
-        <v>2.263197451668475e-08</v>
+        <v>0.03268328309059143</v>
       </c>
       <c r="M9" t="n">
-        <v>3.343096821595282e-08</v>
+        <v>0.1398645043373108</v>
       </c>
       <c r="N9" t="n">
-        <v>1.377614911035607e-08</v>
+        <v>0.05881119519472122</v>
       </c>
       <c r="O9" t="n">
-        <v>7.121316514258069e-08</v>
+        <v>0.1268856525421143</v>
       </c>
       <c r="P9" t="n">
-        <v>1.770820645674576e-08</v>
+        <v>0.01741194911301136</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.759729511581099e-08</v>
+        <v>0.09418398141860962</v>
       </c>
       <c r="R9" t="n">
-        <v>1.563180163088873e-08</v>
+        <v>0.02813216857612133</v>
       </c>
       <c r="S9" t="n">
-        <v>1.191210863282777e-08</v>
+        <v>0.03006737679243088</v>
       </c>
       <c r="T9" t="n">
-        <v>1.814509076325521e-08</v>
+        <v>0.02796092256903648</v>
       </c>
       <c r="U9" t="n">
-        <v>9.111424503771559e-09</v>
+        <v>0.009741161949932575</v>
       </c>
       <c r="V9" t="n">
-        <v>2.622556616316274e-10</v>
+        <v>0.005504543427377939</v>
       </c>
       <c r="W9" t="n">
-        <v>8.861764655421212e-09</v>
+        <v>0.007482969667762518</v>
       </c>
       <c r="X9" t="n">
-        <v>6.844696809338302e-09</v>
+        <v>0.002620695158839226</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.942490943766643e-09</v>
+        <v>0.007909970358014107</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.066309618380501e-08</v>
+        <v>0.01222983282059431</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.718394894913217e-09</v>
+        <v>0.009455216117203236</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.46128414818736e-09</v>
+        <v>0.008614958263933659</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.153332185310774e-08</v>
+        <v>0.05296650156378746</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.594579046582112e-08</v>
+        <v>0.001333058811724186</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.27668524640967e-08</v>
+        <v>0.007346768863499165</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.34097586368398e-08</v>
+        <v>0.01330559700727463</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.343143729570784e-08</v>
+        <v>0.00179103878326714</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.990512643601505e-09</v>
+        <v>0.02692889049649239</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.093618351433179e-08</v>
+        <v>0.005396332126110792</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5.955209658736749e-09</v>
+        <v>0.03772713243961334</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.502929158903044e-08</v>
+        <v>0.03285990655422211</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.253747588554234e-08</v>
+        <v>0.03388906270265579</v>
       </c>
       <c r="AM9" t="n">
-        <v>7.685010849911578e-09</v>
+        <v>0.02059512212872505</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.891616414847704e-10</v>
+        <v>0.001880452036857605</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.378280245489805e-08</v>
+        <v>0.001853039022535086</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.595275436893644e-09</v>
+        <v>0.02907957322895527</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.917073249619762e-09</v>
+        <v>0.006665768101811409</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.017121245704971e-10</v>
+        <v>0.01342780329287052</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.227465862285726e-08</v>
+        <v>0.003806277643889189</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.955734654923162e-09</v>
+        <v>0.02186989784240723</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.587886680620159e-09</v>
+        <v>0.007368495687842369</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.124885653160163e-09</v>
+        <v>0.0008325967937707901</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.021204702553405e-08</v>
+        <v>0.03429060056805611</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.360027195891234e-08</v>
+        <v>0.06222840398550034</v>
       </c>
       <c r="AY9" t="n">
-        <v>2.917181518569123e-08</v>
+        <v>0.05110675469040871</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7.223820430724004e-10</v>
+        <v>0.03000326454639435</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.199591397911149e-09</v>
+        <v>0.02814005687832832</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.414584615057947e-09</v>
+        <v>0.01574187912046909</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.875412405018324e-09</v>
+        <v>0.01100384071469307</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.405335011867464e-09</v>
+        <v>0.04176104813814163</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.769629776049442e-09</v>
+        <v>0.0201965756714344</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.71727493231333e-09</v>
+        <v>0.01824780181050301</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.980665988644887e-09</v>
+        <v>0.03737501427531242</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.028405342637598e-08</v>
+        <v>0.008264591917395592</v>
       </c>
       <c r="BI9" t="n">
-        <v>7.843270921625844e-09</v>
+        <v>0.02532772719860077</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.860670018061228e-08</v>
+        <v>0.03395036235451698</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.097041923969755e-08</v>
+        <v>0.01897523552179337</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.464188059685512e-08</v>
+        <v>0.009110450744628906</v>
       </c>
       <c r="BM9" t="n">
-        <v>3.514658430958661e-08</v>
+        <v>0.053485207259655</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.603301136299251e-08</v>
+        <v>0.01746718212962151</v>
       </c>
       <c r="BO9" t="n">
-        <v>7.353786912744908e-09</v>
+        <v>0.03095183707773685</v>
       </c>
       <c r="BP9" t="n">
-        <v>7.823918402038998e-09</v>
+        <v>0.03225091099739075</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.771535001500069e-09</v>
+        <v>0.01536893658339977</v>
       </c>
       <c r="BR9" t="n">
-        <v>5.588643325893372e-09</v>
+        <v>0.02430037967860699</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.01545036005291e-10</v>
+        <v>0.006661181338131428</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.971609429167302e-09</v>
+        <v>0.005647978745400906</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.718772324466045e-08</v>
+        <v>0.02699323743581772</v>
       </c>
       <c r="BV9" t="n">
-        <v>2.531737486322072e-09</v>
+        <v>0.04096858948469162</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.236899415171024e-09</v>
+        <v>0.01285325363278389</v>
       </c>
       <c r="BX9" t="n">
-        <v>1.539123317684243e-08</v>
+        <v>0.04795902222394943</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.663784748335729e-10</v>
+        <v>0.0247846320271492</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.086375872067947e-08</v>
+        <v>0.02776210010051727</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.485255195556647e-09</v>
+        <v>0.009532948955893517</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.571540840852094e-09</v>
+        <v>0.00633528595790267</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.056962043032854e-09</v>
+        <v>0.00579044921323657</v>
       </c>
       <c r="CD9" t="n">
-        <v>8.02143906852848e-11</v>
+        <v>0.008895466104149818</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.875178679000555e-09</v>
+        <v>0.02000732719898224</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.680709876301535e-09</v>
+        <v>0.001021820586174726</v>
       </c>
       <c r="CG9" t="n">
-        <v>9.733915007359428e-09</v>
+        <v>0.03606381639838219</v>
       </c>
       <c r="CH9" t="n">
-        <v>4.275883203064268e-09</v>
+        <v>0.01863995380699635</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.859747911225895e-08</v>
+        <v>0.02023259736597538</v>
       </c>
       <c r="CJ9" t="n">
-        <v>6.63001320511114e-11</v>
+        <v>0.005238442681729794</v>
       </c>
       <c r="CK9" t="n">
-        <v>5.654094969997914e-09</v>
+        <v>0.008464482612907887</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.282803057696015e-09</v>
+        <v>0.006014652084559202</v>
       </c>
       <c r="CM9" t="n">
-        <v>9.253201760373031e-09</v>
+        <v>0.06660375744104385</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.626546897171011e-09</v>
+        <v>0.01740646176040173</v>
       </c>
       <c r="CO9" t="n">
-        <v>2.94604562967038e-09</v>
+        <v>0.01976342871785164</v>
       </c>
       <c r="CP9" t="n">
-        <v>9.297179914824483e-09</v>
+        <v>0.04127456992864609</v>
       </c>
       <c r="CQ9" t="n">
-        <v>1.603451149634338e-09</v>
+        <v>0.0323474183678627</v>
       </c>
       <c r="CR9" t="n">
-        <v>9.799541178523441e-10</v>
+        <v>0.00364563288167119</v>
       </c>
       <c r="CS9" t="n">
-        <v>1.284706385717982e-08</v>
+        <v>0.02376157976686954</v>
       </c>
       <c r="CT9" t="n">
-        <v>1.1597471427649e-08</v>
+        <v>0.03160488978028297</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.044432984542709e-08</v>
+        <v>0.01107466220855713</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.84272050343759e-09</v>
+        <v>0.006004328839480877</v>
       </c>
       <c r="CW9" t="n">
-        <v>3.186535479926533e-10</v>
+        <v>0.0188303142786026</v>
       </c>
       <c r="CX9" t="n">
-        <v>5.934551072783734e-09</v>
+        <v>0.008555597625672817</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.068410337978776e-08</v>
+        <v>0.03079270012676716</v>
       </c>
       <c r="CZ9" t="n">
-        <v>8.258279393658086e-09</v>
+        <v>0.01503049395978451</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.405543592625236e-08</v>
+        <v>0.02859253436326981</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.821679029845313e-09</v>
+        <v>0.00755577115342021</v>
       </c>
       <c r="DC9" t="n">
-        <v>7.646160149477055e-09</v>
+        <v>0.01161068305373192</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.768825695971145e-09</v>
+        <v>0.005077471490949392</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.955729445057841e-08</v>
+        <v>0.02428702637553215</v>
       </c>
       <c r="DF9" t="n">
-        <v>8.242849958151055e-09</v>
+        <v>0.03243765234947205</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.57350948831936e-08</v>
+        <v>0.00643888209015131</v>
       </c>
       <c r="DH9" t="n">
-        <v>1.797348492260653e-09</v>
+        <v>0.03482500836253166</v>
       </c>
       <c r="DI9" t="n">
-        <v>5.42376366041708e-09</v>
+        <v>0.04625248908996582</v>
       </c>
       <c r="DJ9" t="n">
-        <v>1.333346877352426e-09</v>
+        <v>0.01584181189537048</v>
       </c>
       <c r="DK9" t="n">
-        <v>1.688949602396406e-08</v>
+        <v>0.02524680458009243</v>
       </c>
       <c r="DL9" t="n">
-        <v>1.021796602884706e-08</v>
+        <v>0.03255390003323555</v>
       </c>
       <c r="DM9" t="n">
-        <v>1.367076318814497e-08</v>
+        <v>0.005493997596204281</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.090815970883341e-08</v>
+        <v>0.002549093216657639</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.296840229121244e-08</v>
+        <v>0.02492481470108032</v>
       </c>
       <c r="DP9" t="n">
-        <v>4.093524630377487e-09</v>
+        <v>0.003899113275110722</v>
       </c>
       <c r="DQ9" t="n">
-        <v>8.232232256988326e-11</v>
+        <v>0.00636465847492218</v>
       </c>
       <c r="DR9" t="n">
-        <v>1.834646745635382e-08</v>
+        <v>0.0008663139306008816</v>
       </c>
       <c r="DS9" t="n">
-        <v>1.326978527060874e-08</v>
+        <v>0.003973177634179592</v>
       </c>
       <c r="DT9" t="n">
-        <v>2.528638631815738e-09</v>
+        <v>0.007269134745001793</v>
       </c>
       <c r="DU9" t="n">
-        <v>5.516932688465204e-09</v>
+        <v>0.007370265200734138</v>
       </c>
       <c r="DV9" t="n">
-        <v>1.225006940330786e-08</v>
+        <v>0.05215495452284813</v>
       </c>
       <c r="DW9" t="n">
-        <v>1.327400767081599e-08</v>
+        <v>0.02277695387601852</v>
       </c>
       <c r="DX9" t="n">
-        <v>1.785144121413396e-08</v>
+        <v>0.01973382011055946</v>
       </c>
       <c r="DY9" t="n">
-        <v>2.337220905701543e-08</v>
+        <v>0.007484428118914366</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1.135004623620262e-08</v>
+        <v>0.01035693287849426</v>
       </c>
       <c r="EA9" t="n">
-        <v>5.789515089560382e-09</v>
+        <v>0.02333371341228485</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.065108357067857e-08</v>
+        <v>0.01595022529363632</v>
       </c>
       <c r="EC9" t="n">
-        <v>1.154274098524866e-08</v>
+        <v>0.01182991825044155</v>
       </c>
       <c r="ED9" t="n">
-        <v>2.915393260138899e-09</v>
+        <v>0.007919266819953918</v>
       </c>
       <c r="EE9" t="n">
-        <v>5.656616952620652e-09</v>
+        <v>0.002807080280035734</v>
       </c>
       <c r="EF9" t="n">
-        <v>4.733003322598961e-09</v>
+        <v>0.01024581398814917</v>
       </c>
       <c r="EG9" t="n">
-        <v>5.780755429896089e-09</v>
+        <v>0.03885304182767868</v>
       </c>
       <c r="EH9" t="n">
-        <v>4.906079098532246e-09</v>
+        <v>0.01595803536474705</v>
       </c>
       <c r="EI9" t="n">
-        <v>2.105903718074842e-08</v>
+        <v>0.04713250696659088</v>
       </c>
       <c r="EJ9" t="n">
-        <v>7.412808589180031e-09</v>
+        <v>0.03086943924427032</v>
       </c>
       <c r="EK9" t="n">
-        <v>1.003076288697002e-08</v>
+        <v>0.01682794094085693</v>
       </c>
       <c r="EL9" t="n">
-        <v>4.091550431795099e-10</v>
+        <v>0.01026176568120718</v>
       </c>
       <c r="EM9" t="n">
-        <v>1.095859847310976e-09</v>
+        <v>0.01640157587826252</v>
       </c>
       <c r="EN9" t="n">
-        <v>5.778847622650574e-09</v>
+        <v>0.006987234577536583</v>
       </c>
       <c r="EO9" t="n">
-        <v>9.973240899796565e-09</v>
+        <v>0.008772368542850018</v>
       </c>
       <c r="EP9" t="n">
-        <v>8.104008131226692e-09</v>
+        <v>0.005228294059634209</v>
       </c>
       <c r="EQ9" t="n">
-        <v>1.567742380359505e-08</v>
+        <v>0.0008988534100353718</v>
       </c>
       <c r="ER9" t="n">
-        <v>8.981198007518287e-09</v>
+        <v>0.01466131582856178</v>
       </c>
       <c r="ES9" t="n">
-        <v>1.255956494361499e-08</v>
+        <v>0.02771852724254131</v>
       </c>
       <c r="ET9" t="n">
-        <v>1.110380121183141e-09</v>
+        <v>0.02641230821609497</v>
       </c>
       <c r="EU9" t="n">
-        <v>2.504220830701342e-09</v>
+        <v>0.005842174403369427</v>
       </c>
       <c r="EV9" t="n">
-        <v>1.555549289378177e-08</v>
+        <v>0.005276324693113565</v>
       </c>
       <c r="EW9" t="n">
-        <v>1.539703653463675e-08</v>
+        <v>0.001567064551636577</v>
       </c>
       <c r="EX9" t="n">
-        <v>2.731286752322148e-09</v>
+        <v>0.01018132269382477</v>
       </c>
       <c r="EY9" t="n">
-        <v>9.270363365843082e-10</v>
+        <v>0.02324558794498444</v>
       </c>
       <c r="EZ9" t="n">
-        <v>6.998134516322807e-09</v>
+        <v>0.0001229837071150541</v>
       </c>
       <c r="FA9" t="n">
-        <v>1.295374385534842e-08</v>
+        <v>0.03751145303249359</v>
       </c>
       <c r="FB9" t="n">
-        <v>3.921622138136627e-09</v>
+        <v>0.01854705438017845</v>
       </c>
       <c r="FC9" t="n">
-        <v>1.480226075045721e-08</v>
+        <v>0.02277819626033306</v>
       </c>
       <c r="FD9" t="n">
-        <v>3.366460443743335e-10</v>
+        <v>0.008622697554528713</v>
       </c>
       <c r="FE9" t="n">
-        <v>7.691294712230956e-09</v>
+        <v>0.0158447902649641</v>
       </c>
       <c r="FF9" t="n">
-        <v>1.460665699504204e-09</v>
+        <v>0.003798776306211948</v>
       </c>
       <c r="FG9" t="n">
-        <v>2.203740745443383e-09</v>
+        <v>0.01135051809251308</v>
       </c>
       <c r="FH9" t="n">
-        <v>8.391392469775383e-09</v>
+        <v>0.01721850782632828</v>
       </c>
       <c r="FI9" t="n">
-        <v>2.245441699244566e-08</v>
+        <v>0.01001215633004904</v>
       </c>
       <c r="FJ9" t="n">
-        <v>8.439658749637147e-09</v>
+        <v>0.02039358764886856</v>
       </c>
       <c r="FK9" t="n">
-        <v>2.239373486645491e-08</v>
+        <v>0.02331049926578999</v>
       </c>
       <c r="FL9" t="n">
-        <v>7.094990372991106e-09</v>
+        <v>0.00282844016328454</v>
       </c>
       <c r="FM9" t="n">
-        <v>1.238073021880837e-08</v>
+        <v>0.0004556803032755852</v>
       </c>
       <c r="FN9" t="n">
-        <v>2.471364002332166e-09</v>
+        <v>0.03849870339035988</v>
       </c>
       <c r="FO9" t="n">
-        <v>9.600595873848761e-09</v>
+        <v>0.06605762988328934</v>
       </c>
       <c r="FP9" t="n">
-        <v>1.066047783382373e-08</v>
+        <v>0.07613396644592285</v>
       </c>
       <c r="FQ9" t="n">
-        <v>5.773461264624302e-09</v>
+        <v>0.05176213756203651</v>
       </c>
       <c r="FR9" t="n">
-        <v>6.634990334930535e-10</v>
+        <v>0.02552106603980064</v>
       </c>
       <c r="FS9" t="n">
-        <v>6.205908675838145e-09</v>
+        <v>0.01772556453943253</v>
       </c>
       <c r="FT9" t="n">
-        <v>3.837104856074802e-08</v>
+        <v>0.02279877848923206</v>
       </c>
       <c r="FU9" t="n">
-        <v>9.316960536409624e-09</v>
+        <v>0.01613568887114525</v>
       </c>
       <c r="FV9" t="n">
-        <v>4.873267123173264e-09</v>
+        <v>0.05902631208300591</v>
       </c>
       <c r="FW9" t="n">
-        <v>5.356421972635417e-10</v>
+        <v>0.03667161613702774</v>
       </c>
       <c r="FX9" t="n">
-        <v>7.570021942626681e-09</v>
+        <v>0.02101636119186878</v>
       </c>
       <c r="FY9" t="n">
-        <v>6.451505996096785e-11</v>
+        <v>0.004269396886229515</v>
       </c>
       <c r="FZ9" t="n">
-        <v>2.554378042418648e-08</v>
+        <v>0.0244170892983675</v>
       </c>
       <c r="GA9" t="n">
-        <v>6.755333625818594e-09</v>
+        <v>0.024384506046772</v>
       </c>
       <c r="GB9" t="n">
-        <v>1.391338066980552e-08</v>
+        <v>0.03384693711996078</v>
       </c>
       <c r="GC9" t="n">
-        <v>3.188251795904762e-08</v>
+        <v>0.05038218200206757</v>
       </c>
       <c r="GD9" t="n">
-        <v>1.658880144361774e-08</v>
+        <v>0.0008436099160462618</v>
       </c>
       <c r="GE9" t="n">
-        <v>9.092984143421745e-09</v>
+        <v>0.03211557120084763</v>
       </c>
       <c r="GF9" t="n">
-        <v>2.910104601738794e-09</v>
+        <v>0.02189722284674644</v>
       </c>
       <c r="GG9" t="n">
-        <v>1.601108690074682e-09</v>
+        <v>0.01277633011341095</v>
       </c>
     </row>
     <row r="10">
@@ -7258,1709 +7258,1709 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.02594653330743313</v>
+        <v>0.1080870032310486</v>
       </c>
       <c r="B13" t="n">
-        <v>0.183050736784935</v>
+        <v>0.6714091300964355</v>
       </c>
       <c r="C13" t="n">
-        <v>0.008241485804319382</v>
+        <v>0.1859641224145889</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1095416396856308</v>
+        <v>0.08261465281248093</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004427905660122633</v>
+        <v>0.01980079710483551</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1936004757881165</v>
+        <v>0.3896767199039459</v>
       </c>
       <c r="G13" t="n">
-        <v>0.03156900405883789</v>
+        <v>0.04184672981500626</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05579349398612976</v>
+        <v>0.1677227169275284</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02451140992343426</v>
+        <v>0.1010043546557426</v>
       </c>
       <c r="J13" t="n">
-        <v>0.04736341536045074</v>
+        <v>0.007570624351501465</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1545619070529938</v>
+        <v>1.092005372047424</v>
       </c>
       <c r="L13" t="n">
-        <v>0.009496582671999931</v>
+        <v>0.2062106132507324</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1093218326568604</v>
+        <v>0.2570739090442657</v>
       </c>
       <c r="N13" t="n">
-        <v>0.006944874301552773</v>
+        <v>0.2648775279521942</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1898192167282104</v>
+        <v>0.5067735910415649</v>
       </c>
       <c r="P13" t="n">
-        <v>0.03120847046375275</v>
+        <v>0.3126520812511444</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.007688703015446663</v>
+        <v>0.2397679835557938</v>
       </c>
       <c r="R13" t="n">
-        <v>0.03781427443027496</v>
+        <v>0.1436429023742676</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0008587504271417856</v>
+        <v>0.174120232462883</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01121092587709427</v>
+        <v>0.2102838456630707</v>
       </c>
       <c r="U13" t="n">
-        <v>0.004006870090961456</v>
+        <v>0.1113647297024727</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03362974151968956</v>
+        <v>0.3073510527610779</v>
       </c>
       <c r="W13" t="n">
-        <v>0.02745852246880531</v>
+        <v>0.2828161716461182</v>
       </c>
       <c r="X13" t="n">
-        <v>0.005129704717546701</v>
+        <v>0.10230353474617</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.01475164387375116</v>
+        <v>0.1239018887281418</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.01730952225625515</v>
+        <v>0.2966883480548859</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.01470863539725542</v>
+        <v>0.05556041374802589</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.002809606492519379</v>
+        <v>0.2274799942970276</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01622981764376163</v>
+        <v>0.1021431311964989</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.01074573211371899</v>
+        <v>0.01982670463621616</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.001147765666246414</v>
+        <v>0.160438746213913</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.002222917508333921</v>
+        <v>0.5299165844917297</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.009100724011659622</v>
+        <v>0.2375974953174591</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01074793748557568</v>
+        <v>0.08441638201475143</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.01077694445848465</v>
+        <v>0.132763460278511</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.007983315736055374</v>
+        <v>0.06644582748413086</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.03121046163141727</v>
+        <v>0.05458195507526398</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0153952818363905</v>
+        <v>0.1582215428352356</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.0009272070601582527</v>
+        <v>0.006912112236022949</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.00629238598048687</v>
+        <v>0.2173778265714645</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.001914231106638908</v>
+        <v>0.1347389966249466</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.03814604878425598</v>
+        <v>0.05613007396459579</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.01073731295764446</v>
+        <v>0.1862247288227081</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.01681766845285892</v>
+        <v>0.3359411954879761</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.01955657452344894</v>
+        <v>0.08263819664716721</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.01802416145801544</v>
+        <v>0.1031552255153656</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1322258710861206</v>
+        <v>1.13997483253479</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.003332422580569983</v>
+        <v>0.09318174421787262</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.004391059745103121</v>
+        <v>0.08933207392692566</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.01562215574085712</v>
+        <v>0.1845703274011612</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.09529432654380798</v>
+        <v>0.5241103768348694</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.003254302311688662</v>
+        <v>0.03189714252948761</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.02829441800713539</v>
+        <v>0.09155578911304474</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.03414492309093475</v>
+        <v>0.1187348514795303</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.02808024920523167</v>
+        <v>0.01755014061927795</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04876464977860451</v>
+        <v>0.1008388251066208</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.05746219307184219</v>
+        <v>0.1041034087538719</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.04066373780369759</v>
+        <v>0.03664085268974304</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0465933084487915</v>
+        <v>0.1791220307350159</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.08264850080013275</v>
+        <v>0.05040265619754791</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.008988918736577034</v>
+        <v>0.2098293006420135</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.03018141537904739</v>
+        <v>0.08490306884050369</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.008176347240805626</v>
+        <v>0.02285045757889748</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.006265294272452593</v>
+        <v>0.162101611495018</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.06718330085277557</v>
+        <v>0.186296284198761</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.006156235933303833</v>
+        <v>0.01197364367544651</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.03029975667595863</v>
+        <v>0.1504546999931335</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.03121337853372097</v>
+        <v>0.1118376106023788</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.007268244400620461</v>
+        <v>0.08914056420326233</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.02468958124518394</v>
+        <v>0.08659875392913818</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.007718481589108706</v>
+        <v>0.07151500135660172</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.001965210773050785</v>
+        <v>0.04562250524759293</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.006411222275346518</v>
+        <v>0.2180425226688385</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.07376191765069962</v>
+        <v>0.6761121153831482</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.01401554048061371</v>
+        <v>0.01709321513772011</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.02522969245910645</v>
+        <v>0.4058178067207336</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.00408088369295001</v>
+        <v>0.1749799400568008</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0398564524948597</v>
+        <v>0.2678050100803375</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.01321477442979813</v>
+        <v>0.07332336902618408</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.01341361552476883</v>
+        <v>0.2160314917564392</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.02254737727344036</v>
+        <v>0.06522130966186523</v>
       </c>
       <c r="CD13" t="n">
-        <v>8.434639312326908e-05</v>
+        <v>0.06077396124601364</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.02435356006026268</v>
+        <v>0.2205685377120972</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.01998588070273399</v>
+        <v>0.01883912459015846</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.021976413205266</v>
+        <v>0.0432896763086319</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.01240265183150768</v>
+        <v>0.06612888723611832</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.02442564442753792</v>
+        <v>0.1507011502981186</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.01447606831789017</v>
+        <v>0.09875430166721344</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.009970979765057564</v>
+        <v>0.01845268160104752</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.008454443886876106</v>
+        <v>0.04742433130741119</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.03572115302085876</v>
+        <v>0.1431878507137299</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.02912252955138683</v>
+        <v>0.7332705855369568</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.01569009944796562</v>
+        <v>0.002000622451305389</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.01293124724179506</v>
+        <v>0.2928643226623535</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.002857360057532787</v>
+        <v>0.3649651408195496</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0001762928441166878</v>
+        <v>0.2663361728191376</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.009819403290748596</v>
+        <v>0.1400970816612244</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.02216321229934692</v>
+        <v>0.05021925270557404</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.006350411102175713</v>
+        <v>0.2054478973150253</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.002967183943837881</v>
+        <v>0.02945846319198608</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01946532912552357</v>
+        <v>0.2058064192533493</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.01899825036525726</v>
+        <v>0.01829525083303452</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.02969378232955933</v>
+        <v>0.05048150941729546</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.009572533890604973</v>
+        <v>0.01172822341322899</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.02321767061948776</v>
+        <v>0.1492824107408524</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.01555326767265797</v>
+        <v>0.06436261534690857</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0216187871992588</v>
+        <v>0.002157843671739101</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.000984288053587079</v>
+        <v>0.07494572550058365</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.00118065276183188</v>
+        <v>0.1553487479686737</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.02261322736740112</v>
+        <v>0.05478568375110626</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.005603083409368992</v>
+        <v>0.01471964176744223</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.1063445433974266</v>
+        <v>0.1882429271936417</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0130055183544755</v>
+        <v>0.306257426738739</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.001425793045200408</v>
+        <v>0.02318892255425453</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.01264633610844612</v>
+        <v>0.1537406146526337</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.03735455870628357</v>
+        <v>0.1255115866661072</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.03922990709543228</v>
+        <v>0.003404863178730011</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.01440159138292074</v>
+        <v>0.07975981384515762</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.007051697932183743</v>
+        <v>0.1961049139499664</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.02631133608520031</v>
+        <v>0.009873177856206894</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0009727515280246735</v>
+        <v>0.2082277983427048</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.00377505412325263</v>
+        <v>0.1649021804332733</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.001584405894391239</v>
+        <v>0.04389102756977081</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.01656886003911495</v>
+        <v>0.1705872714519501</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.009745758026838303</v>
+        <v>0.2907124161720276</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.006790590938180685</v>
+        <v>0.0217687226831913</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.001287207938730717</v>
+        <v>0.2162227779626846</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.004675045609474182</v>
+        <v>0.04359159246087074</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.009507110342383385</v>
+        <v>0.06856837868690491</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.009492736309766769</v>
+        <v>0.005839500576257706</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.004257156513631344</v>
+        <v>0.2167187333106995</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.005642826203256845</v>
+        <v>0.2473865300416946</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.003091565798968077</v>
+        <v>0.1141074746847153</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.002930755726993084</v>
+        <v>0.03783304989337921</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.005523025989532471</v>
+        <v>0.09371386468410492</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.01188201829791069</v>
+        <v>0.02894741296768188</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.01228054985404015</v>
+        <v>0.05393976718187332</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0136788934469223</v>
+        <v>0.01840995810925961</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.01031874306499958</v>
+        <v>0.1322822421789169</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0002750074490904808</v>
+        <v>0.1036615744233131</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0219489298760891</v>
+        <v>0.0758378729224205</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.01219760347157717</v>
+        <v>0.09201723337173462</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.000593973440118134</v>
+        <v>0.1094091832637787</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0004736408591270447</v>
+        <v>0.05080253258347511</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.01359651982784271</v>
+        <v>0.005319759249687195</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.003810533555224538</v>
+        <v>0.05752703920006752</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.01548134256154299</v>
+        <v>0.0005342867225408554</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0206542145460844</v>
+        <v>0.1197338029742241</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.001767424400895834</v>
+        <v>0.06790294498205185</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.00533785717561841</v>
+        <v>0.03195756301283836</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.02098597772419453</v>
+        <v>0.1118356436491013</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.05850787833333015</v>
+        <v>0.1749863028526306</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.006047213915735483</v>
+        <v>0.07803215086460114</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.002058274578303099</v>
+        <v>0.0671875849366188</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.01862841844558716</v>
+        <v>0.238935112953186</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.01312001887708902</v>
+        <v>0.01480511948466301</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.02293545007705688</v>
+        <v>0.03125644475221634</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.003868045751005411</v>
+        <v>0.002771146595478058</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0204259566962719</v>
+        <v>0.1698338240385056</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.02225901931524277</v>
+        <v>0.1498667448759079</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.01440641470253468</v>
+        <v>0.04292439669370651</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.01036413572728634</v>
+        <v>0.07089877128601074</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.006164341699331999</v>
+        <v>0.1193147525191307</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.01644081249833107</v>
+        <v>0.22670017182827</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0110213216394186</v>
+        <v>0.04864554852247238</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0256054699420929</v>
+        <v>0.2126152366399765</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.001841549761593342</v>
+        <v>0.2535099983215332</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0353192538022995</v>
+        <v>0.03081207722425461</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.00410360936075449</v>
+        <v>0.2265404015779495</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.01181555353105068</v>
+        <v>0.251213401556015</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.00775749608874321</v>
+        <v>0.1163239106535912</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.01987990736961365</v>
+        <v>0.03147108480334282</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.005099399946630001</v>
+        <v>0.2335656434297562</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.01777661219239235</v>
+        <v>0.08113230764865875</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.04496368765830994</v>
+        <v>0.2155454456806183</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.007178846746683121</v>
+        <v>0.1195410490036011</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.02422348409891129</v>
+        <v>0.0272359736263752</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.01801381632685661</v>
+        <v>0.1816145777702332</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.003142715431749821</v>
+        <v>0.08931930363178253</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01087137218564749</v>
+        <v>0.1785460263490677</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.03579969704151154</v>
+        <v>0.1730972230434418</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.005961209535598755</v>
+        <v>0.06097844615578651</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.002858893945813179</v>
+        <v>0.04574233293533325</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.01393377967178822</v>
+        <v>0.1205103769898415</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.01369616203010082</v>
+        <v>0.01144744083285332</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.03331603482365608</v>
+        <v>0.0008208807557821274</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.07410962134599686</v>
+        <v>0.1348499804735184</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.01543669030070305</v>
+        <v>0.1403992474079132</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.01409998908638954</v>
+        <v>0.2520572543144226</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.01739582419395447</v>
+        <v>0.03176223114132881</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1225171014666557</v>
+        <v>0.5461935997009277</v>
       </c>
       <c r="C14" t="n">
-        <v>0.03627012670040131</v>
+        <v>0.002449728548526764</v>
       </c>
       <c r="D14" t="n">
-        <v>0.09293690323829651</v>
+        <v>0.4838721752166748</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09060946106910706</v>
+        <v>0.2452617883682251</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04173103347420692</v>
+        <v>0.1018144935369492</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01209967955946922</v>
+        <v>0.01136105880141258</v>
       </c>
       <c r="H14" t="n">
-        <v>0.03592085465788841</v>
+        <v>0.1672560274600983</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01336323656141758</v>
+        <v>0.09534849226474762</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001189485192298889</v>
+        <v>0.05536253377795219</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0958871990442276</v>
+        <v>0.5304329395294189</v>
       </c>
       <c r="L14" t="n">
-        <v>0.006382560357451439</v>
+        <v>0.009462684392929077</v>
       </c>
       <c r="M14" t="n">
-        <v>0.08958090841770172</v>
+        <v>0.6006077527999878</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1059978231787682</v>
+        <v>0.5001542568206787</v>
       </c>
       <c r="O14" t="n">
-        <v>0.04530470073223114</v>
+        <v>0.1250912398099899</v>
       </c>
       <c r="P14" t="n">
-        <v>0.01731968112289906</v>
+        <v>0.07033921033143997</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02066472172737122</v>
+        <v>0.07662753760814667</v>
       </c>
       <c r="R14" t="n">
-        <v>0.04236481338739395</v>
+        <v>0.05143187940120697</v>
       </c>
       <c r="S14" t="n">
-        <v>0.009094908833503723</v>
+        <v>0.02115722373127937</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01418207492679358</v>
+        <v>0.02856987901031971</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02562712319195271</v>
+        <v>0.01378243323415518</v>
       </c>
       <c r="V14" t="n">
-        <v>0.02542158402502537</v>
+        <v>0.07707860320806503</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04552386701107025</v>
+        <v>0.02051057294011116</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0109416302293539</v>
+        <v>0.05290753766894341</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.002500920556485653</v>
+        <v>0.02223378978669643</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.002075511729344726</v>
+        <v>0.06058347970247269</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.005285883322358131</v>
+        <v>0.05544355884194374</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.002421138342469931</v>
+        <v>0.02979767508804798</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.01825471222400665</v>
+        <v>0.02295565605163574</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.004134390503168106</v>
+        <v>0.06689954549074173</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.009420808404684067</v>
+        <v>0.2317425906658173</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.04471296817064285</v>
+        <v>0.2891176640987396</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.02133423089981079</v>
+        <v>0.2195578217506409</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.008246872574090958</v>
+        <v>0.04943409934639931</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.01094530150294304</v>
+        <v>0.1852006912231445</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0131064523011446</v>
+        <v>0.01490141730755568</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.001215817872434855</v>
+        <v>0.03865371644496918</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.02044179104268551</v>
+        <v>0.1777741014957428</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.01103698462247849</v>
+        <v>0.05483110249042511</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.02522388845682144</v>
+        <v>0.002594383433461189</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.00695357657968998</v>
+        <v>0.1252860873937607</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.02818670868873596</v>
+        <v>0.05394462123513222</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.001183257205411792</v>
+        <v>0.1505993455648422</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.01523110829293728</v>
+        <v>0.01559635158628225</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.001899586175568402</v>
+        <v>0.01120935287326574</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.002020277082920074</v>
+        <v>0.0564379096031189</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.05851809307932854</v>
+        <v>0.3495012223720551</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.02171608805656433</v>
+        <v>0.01039285305887461</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.01464517042040825</v>
+        <v>0.1040299907326698</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.05146178230643272</v>
+        <v>0.1791780889034271</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.03596299886703491</v>
+        <v>0.05002865940332413</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.01232598535716534</v>
+        <v>0.2236459702253342</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.006547924131155014</v>
+        <v>0.1464319974184036</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.00431715277954936</v>
+        <v>0.01031670998781919</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0007991243619471788</v>
+        <v>0.1211157441139221</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.0296197310090065</v>
+        <v>0.001193253323435783</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.007187649141997099</v>
+        <v>0.1207289844751358</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.05449064075946808</v>
+        <v>0.1509999334812164</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.1032293438911438</v>
+        <v>0.10405233502388</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.03335421904921532</v>
+        <v>0.08827190101146698</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.007202232256531715</v>
+        <v>0.1097780764102936</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.002248603152111173</v>
+        <v>0.157876580953598</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.008849093690514565</v>
+        <v>0.002370547503232956</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.02043861895799637</v>
+        <v>0.004575413651764393</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.002957506105303764</v>
+        <v>0.06671265512704849</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.00149065675213933</v>
+        <v>0.07136774808168411</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.03174590691924095</v>
+        <v>0.06925226002931595</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.009709271602332592</v>
+        <v>0.03106119483709335</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.009735907427966595</v>
+        <v>0.0001574025372974575</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.02685078978538513</v>
+        <v>0.06243886426091194</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.01747332327067852</v>
+        <v>0.1271381378173828</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.01143232174217701</v>
+        <v>0.04398868232965469</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.004080796614289284</v>
+        <v>0.01665589958429337</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.04189237952232361</v>
+        <v>0.234060674905777</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.002670019399374723</v>
+        <v>0.04184603691101074</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.008588122203946114</v>
+        <v>0.3484160900115967</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.03090108744800091</v>
+        <v>0.09839554131031036</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.003301994176581502</v>
+        <v>0.008048171177506447</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0002593882381916046</v>
+        <v>0.1052027642726898</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.004162224475294352</v>
+        <v>0.003767793998122215</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.02148843556642532</v>
+        <v>0.001414241967722774</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.006619773805141449</v>
+        <v>0.01439031306654215</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.01900363899767399</v>
+        <v>0.2081089317798615</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.01334868557751179</v>
+        <v>0.002725608646869659</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.02916395850479603</v>
+        <v>0.1428326219320297</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.007411688566207886</v>
+        <v>0.01451492868363857</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.005699571687728167</v>
+        <v>0.02767171524465084</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.006627552676945925</v>
+        <v>0.08803988993167877</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.006045613903552294</v>
+        <v>0.01519266795367002</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.008827440440654755</v>
+        <v>0.02777132578194141</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.002545265946537256</v>
+        <v>0.06219533085823059</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.002267457544803619</v>
+        <v>0.232322096824646</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0003454731777310371</v>
+        <v>0.2684193253517151</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.03214561939239502</v>
+        <v>0.3392441868782043</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0611860603094101</v>
+        <v>0.07242107391357422</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.01242626365274191</v>
+        <v>0.2049911767244339</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.02614399418234825</v>
+        <v>0.2073817849159241</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.03417515009641647</v>
+        <v>0.01301331631839275</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.01337869372218847</v>
+        <v>0.004659063648432493</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.009475274011492729</v>
+        <v>0.02498381771147251</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.0166039876639843</v>
+        <v>0.1955475658178329</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.01026077568531036</v>
+        <v>0.01126113999634981</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.02178463339805603</v>
+        <v>0.1636121869087219</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.01066161133348942</v>
+        <v>0.0351579375565052</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.008756010793149471</v>
+        <v>0.02734934538602829</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.008632071316242218</v>
+        <v>0.07622458040714264</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.005370620172470808</v>
+        <v>0.01060413010418415</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.01423033140599728</v>
+        <v>0.01874794252216816</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0141077833250165</v>
+        <v>0.001017438946291804</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.05895186215639114</v>
+        <v>0.04331052303314209</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0223921611905098</v>
+        <v>0.007887037470936775</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.02183909714221954</v>
+        <v>0.2416877448558807</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.03770310804247856</v>
+        <v>0.1288510411977768</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.03073627315461636</v>
+        <v>0.01430701836943626</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.003835186362266541</v>
+        <v>0.2242874652147293</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.01407001074403524</v>
+        <v>0.2182310521602631</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.02325740829110146</v>
+        <v>0.06616505235433578</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.01853935234248638</v>
+        <v>0.06782124191522598</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.01189625635743141</v>
+        <v>0.0721101313829422</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.01900124736130238</v>
+        <v>0.05798527598381042</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.04907596111297607</v>
+        <v>0.1424563229084015</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.02688968181610107</v>
+        <v>0.05503951758146286</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0003583456855267286</v>
+        <v>0.01314813643693924</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0005288334796205163</v>
+        <v>0.03651488944888115</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0127538675442338</v>
+        <v>0.1579202264547348</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.001784079940989614</v>
+        <v>0.2864717841148376</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0001736386911943555</v>
+        <v>0.006412789225578308</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.002605181187391281</v>
+        <v>0.01240537129342556</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.009055085480213165</v>
+        <v>0.06348995119333267</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.001293337205424905</v>
+        <v>0.009735614061355591</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.00400620000436902</v>
+        <v>0.1062570363283157</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.04145811498165131</v>
+        <v>0.1198217421770096</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.01460913754999638</v>
+        <v>0.1976997554302216</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.006751874927431345</v>
+        <v>0.2455185502767563</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.007604830432683229</v>
+        <v>0.1584436595439911</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.001201234757900238</v>
+        <v>0.0995342805981636</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.00314877019263804</v>
+        <v>0.1354110240936279</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.006763746030628681</v>
+        <v>0.1155811697244644</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.003603697288781404</v>
+        <v>0.03744779899716377</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.005955937784165144</v>
+        <v>0.1484794169664383</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.003476659534499049</v>
+        <v>0.09491349011659622</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0004490092396736145</v>
+        <v>0.01914473436772823</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.01488324627280235</v>
+        <v>0.03636146709322929</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.01432272419333458</v>
+        <v>0.01965383812785149</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.002506417687982321</v>
+        <v>0.1130638420581818</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.01111998036503792</v>
+        <v>0.2309373617172241</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.01046222355216742</v>
+        <v>0.04953014105558395</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.01524726860225201</v>
+        <v>0.1743026226758957</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.03275192528963089</v>
+        <v>0.08221939951181412</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.02806785702705383</v>
+        <v>0.06800585985183716</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.004464862868189812</v>
+        <v>0.03628594428300858</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.005383383482694626</v>
+        <v>0.1505569964647293</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.004208981990814209</v>
+        <v>0.02939258515834808</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.009874055162072182</v>
+        <v>0.001633062027394772</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.02065583691000938</v>
+        <v>0.2252041548490524</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.01338614989072084</v>
+        <v>0.002360284328460693</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.02736915275454521</v>
+        <v>0.206793487071991</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01024425402283669</v>
+        <v>0.03573988378047943</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.004826478194445372</v>
+        <v>0.02066280692815781</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.01150139234960079</v>
+        <v>0.0824456661939621</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.00197387021034956</v>
+        <v>0.04241200536489487</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.008223317563533783</v>
+        <v>0.006186280399560928</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.006898562423884869</v>
+        <v>0.04179651662707329</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.02221754565834999</v>
+        <v>0.1418642848730087</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.01243068091571331</v>
+        <v>0.05093677341938019</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.006755867507308722</v>
+        <v>0.1578304171562195</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.01698254980146885</v>
+        <v>0.03393623605370522</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.02322106994688511</v>
+        <v>0.07780292630195618</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.00863029807806015</v>
+        <v>0.02650642022490501</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.01717741787433624</v>
+        <v>0.06675168871879578</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.005876578856259584</v>
+        <v>0.1058677509427071</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.01034358143806458</v>
+        <v>0.09260693192481995</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.02320470847189426</v>
+        <v>0.3092626631259918</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.001700305147096515</v>
+        <v>0.05082458257675171</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.01392393279820681</v>
+        <v>0.1235822141170502</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.01730212196707726</v>
+        <v>0.1783650070428848</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.002224976196885109</v>
+        <v>0.03804833069443703</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.05364916101098061</v>
+        <v>0.1193637847900391</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.007474641315639019</v>
+        <v>0.2508908212184906</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.005578420124948025</v>
+        <v>0.127629891037941</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.01369037665426731</v>
+        <v>0.02336553111672401</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0186922699213028</v>
+        <v>0.0604579895734787</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.02013886161148548</v>
+        <v>0.02847845107316971</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.04009548202157021</v>
+        <v>0.1421627998352051</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.08691698312759399</v>
+        <v>0.0810488685965538</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.03447818756103516</v>
+        <v>0.05794470012187958</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.02607595361769199</v>
+        <v>0.05384780839085579</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.009437228552997112</v>
+        <v>0.06422330439090729</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.002903267741203308</v>
+        <v>0.03632881492376328</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3.813833245658316e-05</v>
+        <v>1.581354081281461e-05</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0008717238670215011</v>
+        <v>0.0001547820720588788</v>
       </c>
       <c r="C15" t="n">
-        <v>4.433982030604966e-05</v>
+        <v>6.04877459409181e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0004789138911291957</v>
+        <v>9.817766840569675e-05</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0002347297413507476</v>
+        <v>6.305175338638946e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>5.428594158729538e-05</v>
+        <v>0.0001124010232160799</v>
       </c>
       <c r="G15" t="n">
-        <v>7.363559416262433e-05</v>
+        <v>3.352054045535624e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>5.013261215935927e-06</v>
+        <v>5.570352004724555e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0001554765040054917</v>
+        <v>4.499458009377122e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>5.863846308784559e-05</v>
+        <v>2.623148247948848e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0007404708885587752</v>
+        <v>0.0001694462553132325</v>
       </c>
       <c r="L15" t="n">
-        <v>1.79589133040281e-05</v>
+        <v>4.335744961281307e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0004141148529015481</v>
+        <v>0.0001320833689533174</v>
       </c>
       <c r="N15" t="n">
-        <v>0.000249788659857586</v>
+        <v>4.096473276149482e-07</v>
       </c>
       <c r="O15" t="n">
-        <v>5.798551865154877e-05</v>
+        <v>0.0001183698186650872</v>
       </c>
       <c r="P15" t="n">
-        <v>6.837370165158063e-05</v>
+        <v>4.007197640021332e-05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0002026629081228748</v>
+        <v>2.584414505690802e-05</v>
       </c>
       <c r="R15" t="n">
-        <v>9.143603529082611e-05</v>
+        <v>6.335122452583164e-05</v>
       </c>
       <c r="S15" t="n">
-        <v>3.975254730903544e-05</v>
+        <v>7.718846063653473e-06</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0001274194219149649</v>
+        <v>1.699061613180675e-05</v>
       </c>
       <c r="U15" t="n">
-        <v>5.543028237298131e-06</v>
+        <v>1.469507060392061e-05</v>
       </c>
       <c r="V15" t="n">
-        <v>8.752912981435657e-05</v>
+        <v>3.968802502640756e-06</v>
       </c>
       <c r="W15" t="n">
-        <v>2.087423126795329e-05</v>
+        <v>4.590579010255169e-06</v>
       </c>
       <c r="X15" t="n">
-        <v>2.184077857236844e-05</v>
+        <v>3.474331970210187e-05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0001088435383280739</v>
+        <v>8.705073014425579e-06</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.969340317184106e-05</v>
+        <v>2.501296148693655e-05</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.336850831052288e-05</v>
+        <v>5.025905466027325e-06</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.330551357474178e-05</v>
+        <v>3.630404171417467e-05</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.754154724651016e-05</v>
+        <v>2.237484295619652e-06</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.019874177174643e-05</v>
+        <v>6.020914952387102e-06</v>
       </c>
       <c r="AE15" t="n">
-        <v>6.445495819207281e-05</v>
+        <v>3.464296241872944e-05</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.728485535248183e-05</v>
+        <v>5.002953912480734e-06</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.723903500940651e-05</v>
+        <v>3.916591231245548e-05</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.566217335697729e-05</v>
+        <v>1.438794424757361e-05</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.153573824325576e-05</v>
+        <v>6.442885205615312e-05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.101509719272144e-06</v>
+        <v>2.32749771384988e-05</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0001175893848994747</v>
+        <v>1.495189098932315e-05</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.580730481189676e-05</v>
+        <v>2.389851397310849e-05</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.405312625342049e-05</v>
+        <v>2.697414674912579e-05</v>
       </c>
       <c r="AN15" t="n">
-        <v>8.31207653391175e-05</v>
+        <v>2.487378151272424e-05</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0001020954005070962</v>
+        <v>7.98343444330385e-06</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.0001017940230667591</v>
+        <v>3.531385300448164e-05</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.264549301704392e-05</v>
+        <v>2.003254849114455e-06</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.014702815562487e-05</v>
+        <v>2.131361725332681e-05</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.897128251788672e-05</v>
+        <v>2.567787851148751e-05</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.450990748708136e-05</v>
+        <v>4.362166146165691e-05</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.0005478233215399086</v>
+        <v>4.087045090273023e-05</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.0001794957206584513</v>
+        <v>4.563848051475361e-05</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.000123707897728309</v>
+        <v>3.789190668612719e-05</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.867677257105242e-06</v>
+        <v>0.0001224629086209461</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.000109295651782304</v>
+        <v>0.0001001956989057362</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.109644654206932e-05</v>
+        <v>7.289916538866237e-06</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.996346878120676e-05</v>
+        <v>2.568016316217836e-05</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.241265924065374e-05</v>
+        <v>4.210164843243547e-05</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.673875522101298e-05</v>
+        <v>8.440591955150012e-06</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.764805872691795e-05</v>
+        <v>4.634166180039756e-05</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.0001815223949961364</v>
+        <v>8.850000995153096e-06</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.0001089595607481897</v>
+        <v>5.837615390191786e-05</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.0001780784368747845</v>
+        <v>8.175305993063375e-05</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.022636155947112e-05</v>
+        <v>2.165280784538481e-05</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.175788879161701e-05</v>
+        <v>1.104779039451387e-05</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.0001380722533212975</v>
+        <v>4.855293445871212e-05</v>
       </c>
       <c r="BK15" t="n">
-        <v>6.492209649877623e-05</v>
+        <v>1.105095816456014e-05</v>
       </c>
       <c r="BL15" t="n">
-        <v>7.688969344599172e-05</v>
+        <v>1.174523822555784e-05</v>
       </c>
       <c r="BM15" t="n">
-        <v>9.515943384030834e-05</v>
+        <v>2.635268174344674e-05</v>
       </c>
       <c r="BN15" t="n">
-        <v>2.809650504786987e-05</v>
+        <v>1.171749681816436e-05</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.983711808861699e-05</v>
+        <v>1.32458690131898e-05</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0001216250602738</v>
+        <v>1.325034645560663e-05</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8.051608165260404e-05</v>
+        <v>1.38638133648783e-05</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.000100643650512211</v>
+        <v>1.964021066669375e-05</v>
       </c>
       <c r="BS15" t="n">
-        <v>4.552085374598391e-05</v>
+        <v>1.09461334432126e-05</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.225889956112951e-05</v>
+        <v>1.545112172607332e-05</v>
       </c>
       <c r="BU15" t="n">
-        <v>2.81119100691285e-05</v>
+        <v>1.778574733179994e-05</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.0003018378629349172</v>
+        <v>2.730540836637374e-05</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.335737660061568e-05</v>
+        <v>3.391506834304892e-05</v>
       </c>
       <c r="BX15" t="n">
-        <v>3.464195469859987e-05</v>
+        <v>2.484998913132586e-05</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.173044595110696e-05</v>
+        <v>2.230343852716032e-05</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.739112435141578e-05</v>
+        <v>5.302712816046551e-05</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.631834599422291e-05</v>
+        <v>1.293507739319466e-05</v>
       </c>
       <c r="CB15" t="n">
-        <v>6.976590157137252e-06</v>
+        <v>1.705979047983419e-05</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.427368372082128e-06</v>
+        <v>1.023229287966387e-05</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.006283441209234e-05</v>
+        <v>1.328227335761767e-05</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.0001539972727186978</v>
+        <v>4.554277256829664e-05</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.342555282870308e-05</v>
+        <v>3.593564088077983e-06</v>
       </c>
       <c r="CG15" t="n">
-        <v>5.342702206689864e-05</v>
+        <v>3.215917968191206e-05</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.184035500045866e-05</v>
+        <v>1.266948856937233e-05</v>
       </c>
       <c r="CI15" t="n">
-        <v>6.950179340492468e-06</v>
+        <v>2.042169217020273e-05</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.402008183504222e-05</v>
+        <v>3.50379423252889e-06</v>
       </c>
       <c r="CK15" t="n">
-        <v>2.983025842695497e-05</v>
+        <v>2.998139098053798e-05</v>
       </c>
       <c r="CL15" t="n">
-        <v>4.112193710170686e-05</v>
+        <v>1.37848655867856e-06</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.0001968324941117316</v>
+        <v>1.62515789270401e-07</v>
       </c>
       <c r="CN15" t="n">
-        <v>4.865785376750864e-05</v>
+        <v>2.303585824847687e-05</v>
       </c>
       <c r="CO15" t="n">
-        <v>7.729730896244291e-06</v>
+        <v>4.612647899193689e-05</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.0001324185577686876</v>
+        <v>5.71341224713251e-05</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.0001871630665846169</v>
+        <v>7.782222382957116e-05</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.0001869350380729884</v>
+        <v>3.330367326270789e-05</v>
       </c>
       <c r="CS15" t="n">
-        <v>9.941063035512343e-05</v>
+        <v>3.535261839715531e-06</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0001033051303238608</v>
+        <v>2.415771450614557e-05</v>
       </c>
       <c r="CU15" t="n">
-        <v>8.816364425001666e-05</v>
+        <v>4.589658055920154e-05</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.059150756394956e-05</v>
+        <v>1.680275454418734e-05</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.0001553567417431623</v>
+        <v>4.225401789881289e-05</v>
       </c>
       <c r="CX15" t="n">
-        <v>5.512605639523827e-05</v>
+        <v>5.740414053434506e-06</v>
       </c>
       <c r="CY15" t="n">
-        <v>8.939077088143677e-05</v>
+        <v>3.512845432851464e-05</v>
       </c>
       <c r="CZ15" t="n">
-        <v>1.670872734393924e-05</v>
+        <v>5.230655006016605e-06</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.636924753256608e-05</v>
+        <v>2.873846460715868e-05</v>
       </c>
       <c r="DB15" t="n">
-        <v>2.178574868594296e-05</v>
+        <v>1.097786707759951e-06</v>
       </c>
       <c r="DC15" t="n">
-        <v>3.67033171642106e-05</v>
+        <v>2.325016976101324e-05</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.926974750356749e-05</v>
+        <v>1.784337655408308e-07</v>
       </c>
       <c r="DE15" t="n">
-        <v>9.012269583763555e-05</v>
+        <v>1.354442065348849e-05</v>
       </c>
       <c r="DF15" t="n">
-        <v>9.614591544959694e-05</v>
+        <v>3.246085543651134e-05</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.704476355575025e-05</v>
+        <v>2.207509896834381e-05</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.0001294243411393836</v>
+        <v>1.090703972295159e-05</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0001129332886193879</v>
+        <v>6.217879126779735e-05</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.764792225207202e-05</v>
+        <v>6.598036270588636e-05</v>
       </c>
       <c r="DK15" t="n">
-        <v>2.24813829845516e-05</v>
+        <v>1.517165492259664e-05</v>
       </c>
       <c r="DL15" t="n">
-        <v>1.373392206005519e-05</v>
+        <v>5.485264409799129e-06</v>
       </c>
       <c r="DM15" t="n">
-        <v>9.396062523592263e-05</v>
+        <v>1.754018012434244e-05</v>
       </c>
       <c r="DN15" t="n">
-        <v>5.503359716385603e-05</v>
+        <v>1.929094651131891e-05</v>
       </c>
       <c r="DO15" t="n">
-        <v>4.063062806380913e-05</v>
+        <v>2.240435787825845e-05</v>
       </c>
       <c r="DP15" t="n">
-        <v>4.085634827788454e-06</v>
+        <v>2.085136111418251e-05</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.0001468714617658406</v>
+        <v>2.791081533359829e-05</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.377400520956144e-05</v>
+        <v>1.667276592343114e-05</v>
       </c>
       <c r="DS15" t="n">
-        <v>2.958770892291795e-05</v>
+        <v>3.982607267971616e-06</v>
       </c>
       <c r="DT15" t="n">
-        <v>2.707106978050433e-05</v>
+        <v>1.84612854354782e-05</v>
       </c>
       <c r="DU15" t="n">
-        <v>4.142540637985803e-05</v>
+        <v>3.947735240217298e-05</v>
       </c>
       <c r="DV15" t="n">
-        <v>3.968840246670879e-05</v>
+        <v>1.501430233474821e-05</v>
       </c>
       <c r="DW15" t="n">
-        <v>1.469722974434262e-05</v>
+        <v>1.33672938318341e-05</v>
       </c>
       <c r="DX15" t="n">
-        <v>7.902245124569163e-05</v>
+        <v>2.388971188338473e-05</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.293469778029248e-05</v>
+        <v>2.048130227194633e-05</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.020961205242202e-05</v>
+        <v>4.184498720860574e-06</v>
       </c>
       <c r="EA15" t="n">
-        <v>8.764781523495913e-05</v>
+        <v>2.057229266938521e-06</v>
       </c>
       <c r="EB15" t="n">
-        <v>2.924721002273145e-06</v>
+        <v>1.863700163085014e-05</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.0001101773959817365</v>
+        <v>6.942879736016039e-06</v>
       </c>
       <c r="ED15" t="n">
-        <v>3.74598239432089e-05</v>
+        <v>4.858960892306641e-05</v>
       </c>
       <c r="EE15" t="n">
-        <v>6.980430043768138e-05</v>
+        <v>1.263624653802253e-05</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.0001286767364945263</v>
+        <v>6.598939307878027e-06</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0002002713736146688</v>
+        <v>5.928846076130867e-05</v>
       </c>
       <c r="EH15" t="n">
-        <v>9.826145833358169e-05</v>
+        <v>3.586056664062198e-06</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.0001074829342542216</v>
+        <v>8.022710062505212e-06</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.000120613090984989</v>
+        <v>9.896265510178637e-06</v>
       </c>
       <c r="EK15" t="n">
-        <v>3.596683200157713e-07</v>
+        <v>7.822556653991342e-06</v>
       </c>
       <c r="EL15" t="n">
-        <v>2.074700205412228e-05</v>
+        <v>2.468515504006064e-06</v>
       </c>
       <c r="EM15" t="n">
-        <v>1.71902993315598e-05</v>
+        <v>1.98385623662034e-06</v>
       </c>
       <c r="EN15" t="n">
-        <v>2.243048402306158e-05</v>
+        <v>1.103049271478085e-05</v>
       </c>
       <c r="EO15" t="n">
-        <v>2.425008278805763e-05</v>
+        <v>2.623018190206494e-05</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.000111172121251002</v>
+        <v>2.37381063925568e-05</v>
       </c>
       <c r="EQ15" t="n">
-        <v>5.797431367682293e-05</v>
+        <v>6.96909410180524e-06</v>
       </c>
       <c r="ER15" t="n">
-        <v>6.196140748215839e-05</v>
+        <v>3.874116373481229e-05</v>
       </c>
       <c r="ES15" t="n">
-        <v>1.504721240053186e-05</v>
+        <v>3.613659282564186e-05</v>
       </c>
       <c r="ET15" t="n">
-        <v>7.455763261532411e-05</v>
+        <v>2.173588291043416e-05</v>
       </c>
       <c r="EU15" t="n">
-        <v>6.201009091455489e-05</v>
+        <v>1.396434163325466e-05</v>
       </c>
       <c r="EV15" t="n">
-        <v>1.562694160384126e-05</v>
+        <v>3.681864473037422e-05</v>
       </c>
       <c r="EW15" t="n">
-        <v>3.178084443788975e-05</v>
+        <v>4.705156698037172e-06</v>
       </c>
       <c r="EX15" t="n">
-        <v>4.822884511668235e-05</v>
+        <v>1.39637468237197e-05</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.0001587687147548422</v>
+        <v>5.232827243162319e-05</v>
       </c>
       <c r="EZ15" t="n">
-        <v>4.291954974178225e-05</v>
+        <v>4.780616109201219e-06</v>
       </c>
       <c r="FA15" t="n">
-        <v>6.388530164258555e-05</v>
+        <v>3.822360304184258e-05</v>
       </c>
       <c r="FB15" t="n">
-        <v>1.673066435614601e-05</v>
+        <v>8.173149581125472e-06</v>
       </c>
       <c r="FC15" t="n">
-        <v>1.135767524829134e-05</v>
+        <v>1.925046308315359e-05</v>
       </c>
       <c r="FD15" t="n">
-        <v>7.328435458475724e-06</v>
+        <v>4.244544015818974e-06</v>
       </c>
       <c r="FE15" t="n">
-        <v>1.617332054593135e-05</v>
+        <v>2.942267383332364e-05</v>
       </c>
       <c r="FF15" t="n">
-        <v>4.996218922315165e-05</v>
+        <v>1.229417648573872e-06</v>
       </c>
       <c r="FG15" t="n">
-        <v>5.813999086967669e-05</v>
+        <v>7.437809017574182e-06</v>
       </c>
       <c r="FH15" t="n">
-        <v>1.432246699550888e-05</v>
+        <v>4.755655390908942e-05</v>
       </c>
       <c r="FI15" t="n">
-        <v>8.944458386395127e-05</v>
+        <v>4.039668419864029e-05</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.0001001203927444294</v>
+        <v>9.037492418428883e-06</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0001214802541653626</v>
+        <v>6.552452759933658e-06</v>
       </c>
       <c r="FL15" t="n">
-        <v>7.199738320196047e-05</v>
+        <v>3.215067408746108e-05</v>
       </c>
       <c r="FM15" t="n">
-        <v>7.809509042999707e-06</v>
+        <v>4.67276549898088e-07</v>
       </c>
       <c r="FN15" t="n">
-        <v>4.508902293309802e-06</v>
+        <v>3.543938873917796e-05</v>
       </c>
       <c r="FO15" t="n">
-        <v>3.922159521607682e-07</v>
+        <v>1.527157564851223e-06</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0001404975773766637</v>
+        <v>7.505550456698984e-07</v>
       </c>
       <c r="FQ15" t="n">
-        <v>1.89856600627536e-05</v>
+        <v>2.112215952365659e-05</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.0002042896376224235</v>
+        <v>8.282589260488749e-05</v>
       </c>
       <c r="FS15" t="n">
-        <v>3.38575555360876e-05</v>
+        <v>2.078977195196785e-05</v>
       </c>
       <c r="FT15" t="n">
-        <v>2.575722101028077e-05</v>
+        <v>4.121336314710788e-05</v>
       </c>
       <c r="FU15" t="n">
-        <v>1.962738315341994e-05</v>
+        <v>3.435365215409547e-05</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.000102283651358448</v>
+        <v>1.79173621290829e-05</v>
       </c>
       <c r="FW15" t="n">
-        <v>4.869638360105455e-05</v>
+        <v>3.931011451641098e-05</v>
       </c>
       <c r="FX15" t="n">
-        <v>9.713178587844595e-05</v>
+        <v>9.285822670790367e-06</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.0001200180558953434</v>
+        <v>8.638458893983625e-06</v>
       </c>
       <c r="FZ15" t="n">
-        <v>3.085259231738746e-05</v>
+        <v>1.539360891911201e-05</v>
       </c>
       <c r="GA15" t="n">
-        <v>6.192740693222731e-05</v>
+        <v>3.581022974685766e-05</v>
       </c>
       <c r="GB15" t="n">
-        <v>4.531495869741775e-05</v>
+        <v>5.911771495448193e-06</v>
       </c>
       <c r="GC15" t="n">
-        <v>1.013255132420454e-05</v>
+        <v>2.886947731894907e-05</v>
       </c>
       <c r="GD15" t="n">
-        <v>8.807535050436854e-05</v>
+        <v>5.012205656385049e-05</v>
       </c>
       <c r="GE15" t="n">
-        <v>8.919843094190583e-05</v>
+        <v>1.241802237927914e-06</v>
       </c>
       <c r="GF15" t="n">
-        <v>6.542181654367596e-05</v>
+        <v>5.32799786014948e-05</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.0001398453459842131</v>
+        <v>1.999092637561262e-05</v>
       </c>
     </row>
   </sheetData>
